--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>134.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.9%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.5%</t>
+          <t>-607.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-59.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.8%</t>
+          <t>-280.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.4%</t>
+          <t>-153.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.2%</t>
+          <t>-267.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-203.0%</t>
+          <t>-198.0%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.019262155608931</v>
+        <v>-5.913593271654345</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7093631743657616</v>
+        <v>0.751630727947596</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.036309959284833</v>
+        <v>-0.9545487057869879</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.495638485352182</v>
+        <v>2.544695237450889</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.384389538247677</v>
+        <v>-6.278720654293092</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5625667363160942</v>
+        <v>0.6048342898979286</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.332620743583846</v>
+        <v>-1.250859490086</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.317106529778606</v>
+        <v>2.366163281877313</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.792978315428355</v>
+        <v>-6.68730943147377</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3978927694585823</v>
+        <v>0.4401603230404163</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.070714807484958</v>
+        <v>2.119771559583665</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.205960799569449</v>
+        <v>-7.100291915614863</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2278852082736051</v>
+        <v>0.2701527618554396</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.065900239956418</v>
+        <v>2.114956992055125</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.622352673856446</v>
+        <v>-7.516683789901861</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.05932250916768389</v>
+        <v>0.1015900627495179</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.063894290565296</v>
+        <v>2.112951042664003</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.999029684386291</v>
+        <v>-7.893360800431705</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08108960437557489</v>
+        <v>-0.0388220507937409</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.074152981233975</v>
+        <v>2.123209733332682</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.344904506371099</v>
+        <v>-8.239235622416514</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2233399680238031</v>
+        <v>-0.1810724144419691</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.070252546379669</v>
+        <v>2.119309298478377</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.401377892879607</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.2475244025722052</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.06865746643467</v>
+        <v>2.117714218533378</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.698039234689805</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.3624099633670763</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.728191403000557</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.031190560923552</v>
+        <v>2.080247313022259</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.13138834280004</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5397759111455738</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.728191403000557</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.027164256389149</v>
+        <v>2.076221008487856</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.514389731542671</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.6930785679642102</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.728191403000557</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.027062155067564</v>
+        <v>2.076118907166272</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.671788611755792</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.7534666040780285</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.885590283213679</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935194342911122</v>
+        <v>1.984251095009829</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-10.03131893425979</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.8919284297815784</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.885590283213679</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.940544646209172</v>
+        <v>1.98960139830788</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.35771896292481</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-1.014572421290407</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.293751565376537</v>
+        <v>-2.211990311878691</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.752620648967342</v>
+        <v>1.801677401066049</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.576867930999</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.099190257898317</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.431139279952889</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.624173018744592</v>
+        <v>1.673229770843299</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.57317700604259</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.097713887915753</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.431139279952889</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.624173018744592</v>
+        <v>1.673229770843299</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.77743518137246</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.173903960929056</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.640539478064723</v>
+        <v>-2.558778224566878</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.553102849094841</v>
+        <v>1.602159601193548</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-10.99547295300363</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.25663651509709</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.815310246160622</v>
+        <v>-2.733548992662777</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.452722942721738</v>
+        <v>1.501779694820445</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-10.92200312133619</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.21187688093669</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.741840414493173</v>
+        <v>-2.660079160995328</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.512176543215628</v>
+        <v>1.561233295314335</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.09712753872273</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.26737142714379</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.835203578381872</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.421657113531219</v>
+        <v>1.470713865629926</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.33157963273722</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.368371429651182</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.835203578381872</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.414437948629623</v>
+        <v>1.46349470072833</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.61938347727446</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.490165158240054</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.204768676416955</v>
+        <v>-3.12300742291911</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.235083451133304</v>
+        <v>1.284140203232011</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.84920792443828</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.580979147267027</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.367416213487116</v>
+        <v>-3.285654959989271</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.138610718729764</v>
+        <v>1.187667470828471</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.08123684417454</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.671096986532417</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.347667657177694</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.104096829045825</v>
+        <v>1.153153581144532</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-12.02922133020573</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.646300445258492</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.347667657177694</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.108087164732225</v>
+        <v>1.157143916830933</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.17089317192985</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.704444408846881</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.347667657177694</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.106611937833484</v>
+        <v>1.155668689932191</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.12130232750502</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.669554660912075</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.379838066250705</v>
+        <v>-3.29807681275286</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.151419854653256</v>
+        <v>1.200476606751963</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-11.92215022026792</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.602944951663919</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.214515540300892</v>
+        <v>-3.132754286803047</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.237562236576461</v>
+        <v>1.286618988675168</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.69630506754851</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.503027817539946</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.090827611215883</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.272297314964968</v>
+        <v>1.321354067063675</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.57172641121092</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.45205721044885</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.090827611215883</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.273436459521027</v>
+        <v>1.322493211619734</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.6246216992552</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.470581551504457</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.085872265127437</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.279043441336202</v>
+        <v>1.328100193434909</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.34071296832645</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.351284354894321</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.085872265127437</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.284777145574839</v>
+        <v>1.333833897673546</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37501545967139</v>
+        <v>-11.26934657571681</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.374742613826162</v>
+        <v>-1.332475060244327</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.014505872517789</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.317859718746762</v>
+        <v>1.36691647084547</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-11.00550970851274</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.236823794675607</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.014505872517789</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.307976237433855</v>
+        <v>1.357032989532562</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84393679159892</v>
+        <v>-10.73826790764434</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174029188409456</v>
+        <v>-1.131761634827622</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.014505872517789</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.306141676934481</v>
+        <v>1.355198429033188</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.72063086312071</v>
+        <v>-10.61496197916612</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.125007131991629</v>
+        <v>-1.082739578409795</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.006849454888072</v>
+        <v>-2.925088201390226</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.359491964637558</v>
+        <v>1.408548716736265</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.69667732214475</v>
+        <v>-10.59100843819016</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.114757209455753</v>
+        <v>-1.072489655873918</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.982895913912114</v>
+        <v>-2.901134660414269</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.374532595368626</v>
+        <v>1.423589347467333</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.43261738382195</v>
+        <v>-10.32694849986737</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.022393550288386</v>
+        <v>-0.9801259967065512</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.637074722091473</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.519708242200551</v>
+        <v>1.568764994299259</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.725537760317113</v>
+        <v>-9.619868876362528</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7423487345467517</v>
+        <v>-0.7000811809649177</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.637074722091473</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.516921208540251</v>
+        <v>1.565977960638958</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.685353461950923</v>
+        <v>-9.579684577996337</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7259313913124341</v>
+        <v>-0.6836638377306001</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.678651677223127</v>
+        <v>-2.596890423725282</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.541375411447807</v>
+        <v>1.590432163546514</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.605283666413118</v>
+        <v>-9.499614782458533</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6945366518765557</v>
+        <v>-0.6522690982947212</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.598581881685323</v>
+        <v>-2.516820628187478</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.588784109991246</v>
+        <v>1.637840862089953</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.371802444183519</v>
+        <v>-9.266133560228933</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5932197341468632</v>
+        <v>-0.5509521805650293</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.365100659455724</v>
+        <v>-2.283339405957879</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.736797272166857</v>
+        <v>1.785854024265564</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.192093914039646</v>
+        <v>-9.08642503008506</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5242285324022733</v>
+        <v>-0.4819609788204389</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.307929155293028</v>
+        <v>-2.226167901795183</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.768207964351516</v>
+        <v>1.817264716450223</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.059818440408758</v>
+        <v>-8.954149556454173</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4759508562028913</v>
+        <v>-0.4336833026210569</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.175653681662142</v>
+        <v>-2.093892428164297</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.842940735277075</v>
+        <v>1.891997487375782</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.869218765735605</v>
+        <v>-8.763549881781019</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.396895925645993</v>
+        <v>-0.354628372064159</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.985054006988989</v>
+        <v>-1.903292753491144</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.960115600768603</v>
+        <v>2.00917235286731</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.620218967052024</v>
+        <v>-8.514550083097438</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2843896649489017</v>
+        <v>-0.2421221113670677</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.985054006988989</v>
+        <v>-1.903292753491144</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.973021941992262</v>
+        <v>2.022078694090969</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.725808956825128</v>
+        <v>-8.620140072870543</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4546015904573624</v>
+        <v>-0.4123340368755279</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.008882743264248</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.781692018529181</v>
+        <v>1.830748770627888</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.744543858943725</v>
+        <v>-8.63887497498914</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4135512094277147</v>
+        <v>-0.3712836558458807</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.008882743264248</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.830236360406267</v>
+        <v>1.879293112504974</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.596603817536126</v>
+        <v>-8.49093493358154</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4742541155528426</v>
+        <v>-0.4319865619710086</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.070323080853536</v>
+        <v>-1.988561827355691</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.722549987263234</v>
+        <v>1.771606739361941</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.572375181147153</v>
+        <v>-8.466706297192568</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4732766472507319</v>
+        <v>-0.4310090936688975</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.046094444464564</v>
+        <v>-1.964333190966718</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.728373182843139</v>
+        <v>1.777429934941846</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.528826774376462</v>
+        <v>-8.423157890421876</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4628178966375485</v>
+        <v>-0.420550343055714</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.046094444464564</v>
+        <v>-1.964333190966718</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.721412570748046</v>
+        <v>1.770469322846753</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.286678380922604</v>
+        <v>-8.181009496968018</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3514961848748621</v>
+        <v>-0.3092286312930277</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.046094444464564</v>
+        <v>-1.964333190966718</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.735874925129189</v>
+        <v>1.784931677227896</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.223449009154256</v>
+        <v>-8.117780125199671</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3316723157083281</v>
+        <v>-0.2894047621264937</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.046094444464564</v>
+        <v>-1.964333190966718</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.730407045588384</v>
+        <v>1.779463797687091</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.100157874337127</v>
+        <v>-7.99448899038254</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2848577677708994</v>
+        <v>-0.2425902141890646</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.922803309647434</v>
+        <v>-1.841042056149588</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.801879820489239</v>
+        <v>1.850936572587946</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.079008675433684</v>
+        <v>-7.973339791479097</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2686971099721971</v>
+        <v>-0.2264295563903622</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.819892857246145</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.82227031806863</v>
+        <v>1.871327070167337</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.83524323345024</v>
+        <v>-7.729574349495652</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1754102248317686</v>
+        <v>-0.1331426712499337</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.819892857246145</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.818051026415681</v>
+        <v>1.867107778514388</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.57121516625698</v>
+        <v>-7.465546282302393</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.06767468403444887</v>
+        <v>-0.025407130452614</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.618027458430191</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.941294579625269</v>
+        <v>1.990351331723976</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.321364772307906</v>
+        <v>-7.215695888353318</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.02500754852888321</v>
+        <v>0.06727510211071808</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.618027458430191</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.934036654608971</v>
+        <v>1.983093406707678</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.145472679840474</v>
+        <v>-7.039803795885886</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.09896350903650486</v>
+        <v>0.1412310626183397</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.618027458430191</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.93763577812962</v>
+        <v>1.986692530228327</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.97402621681801</v>
+        <v>-6.868357332863423</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1808696003000438</v>
+        <v>0.2231371538818787</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.528342248905573</v>
+        <v>-1.446580995407728</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.053831161997651</v>
+        <v>2.102887914096359</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.748993217149187</v>
+        <v>-6.6433243331946</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2699032777838699</v>
+        <v>0.3121708313657048</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.30330924923675</v>
+        <v>-1.221547995738905</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.187871439415242</v>
+        <v>2.236928191513949</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.53435883951278</v>
+        <v>-6.428689955558193</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3604518298927499</v>
+        <v>0.4027193834745848</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.006913618102498</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.321346867051404</v>
+        <v>2.370403619150111</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.441358798306882</v>
+        <v>-6.335689914352295</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3788461051589049</v>
+        <v>0.4211136587407398</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.006913618102498</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.302541125835199</v>
+        <v>2.351597877933906</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.200928301502022</v>
+        <v>-6.095259417547434</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4767613805057263</v>
+        <v>0.5190289340875611</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.7664831212976377</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.448542500542993</v>
+        <v>2.4975992526417</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.958137493852576</v>
+        <v>-5.852468609897989</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5778070174003247</v>
+        <v>0.6200745709821596</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.7664831212976377</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.452471814377813</v>
+        <v>2.50152856647652</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.842197644227391</v>
+        <v>-5.736528760272804</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6248615411677387</v>
+        <v>0.667129094749574</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.6896613902815139</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.499243436904827</v>
+        <v>2.548300189003534</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.599542055804228</v>
+        <v>-5.493873171849641</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7189218477569974</v>
+        <v>0.7611894013388323</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.6896613902815139</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.496241508124821</v>
+        <v>2.545298260223528</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.379521257767218</v>
+        <v>-5.27385237381263</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8085092039824158</v>
+        <v>0.8507767575642506</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.5484415452135336</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.582552452176223</v>
+        <v>2.63160920427493</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.180272627862409</v>
+        <v>-5.074603743907821</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9041028387461627</v>
+        <v>0.9463703923279976</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.5484415452135336</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.598446634978046</v>
+        <v>2.647503387076754</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.020757524343039</v>
+        <v>-4.915088640388452</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9690547245942125</v>
+        <v>1.011322278176048</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4706876951920093</v>
+        <v>-0.3889264416941637</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.69530154152997</v>
+        <v>2.744358293628677</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.876085379243301</v>
+        <v>-4.770416495288714</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.037011685195548</v>
+        <v>1.079279238777382</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3260155500922718</v>
+        <v>-0.2442542965944263</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.792192931151253</v>
+        <v>2.84124968324996</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.935960206600994</v>
+        <v>-4.830291322646406</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9990992456538963</v>
+        <v>1.041366799235731</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.3041291239521184</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.742305526138063</v>
+        <v>2.79136227823677</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.849160708821985</v>
+        <v>-4.743491824867398</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.056219538088066</v>
+        <v>1.098487091669901</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.3041291239521184</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.764706019460629</v>
+        <v>2.813762771559337</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.851630415283791</v>
+        <v>-4.745961531329204</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.055304056876756</v>
+        <v>1.09757161045859</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3883600839117701</v>
+        <v>-0.3065988304139246</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.763296596956958</v>
+        <v>2.812353349055665</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.920000601607802</v>
+        <v>-4.814331717653214</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.038962904821853</v>
+        <v>1.081230458403688</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.779868938853388</v>
+        <v>2.828925690952096</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.798584171981325</v>
+        <v>-4.692915288026738</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.077966185304335</v>
+        <v>1.12023373888617</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.77030564748528</v>
+        <v>2.819362399583987</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.829577331310031</v>
+        <v>-4.723908447355443</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.89027848661324</v>
+        <v>0.9325460401950749</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.595015212525666</v>
+        <v>2.644071964624374</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.654103071517561</v>
+        <v>-4.548434187562973</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9650354225220157</v>
+        <v>1.007302976103851</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.599582444517454</v>
+        <v>2.648639196616162</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.76503932415881</v>
+        <v>-4.659370440204222</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9206723953523137</v>
+        <v>0.9629399489341486</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.599593918404252</v>
+        <v>2.648650670502959</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.968065901702043</v>
+        <v>-4.862397017747456</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8425931495549259</v>
+        <v>0.8848607031367608</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.500349708920943</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.480909357098217</v>
+        <v>2.529966109196925</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.81014030276675</v>
+        <v>-4.704471418812163</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9159357755611754</v>
+        <v>0.9582033291430103</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.500349708920943</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.49108174353035</v>
+        <v>2.540138495629057</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.958461556577879</v>
+        <v>-4.852792672623291</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8515535446105842</v>
+        <v>0.8938210981924193</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.500349708920943</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.48602801410421</v>
+        <v>2.535084766202917</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.959644641228939</v>
+        <v>-4.853975757274352</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8428560861946857</v>
+        <v>0.8851236397765205</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.5059927573874545</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.474417960468829</v>
+        <v>2.523474712567536</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.836516934234856</v>
+        <v>-4.730848050280269</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8926590420254203</v>
+        <v>0.9349265956072554</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.5059927573874545</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.47496983350193</v>
+        <v>2.524026585600638</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.743706452783996</v>
+        <v>-4.638037568829409</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8590559264971298</v>
+        <v>0.9013234800789649</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4949435294344408</v>
+        <v>-0.4131822759365952</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.459928814263812</v>
+        <v>2.508985566362519</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.695143400562967</v>
+        <v>-4.589474516608379</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8803546233101427</v>
+        <v>0.9226221768919776</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4463804772134106</v>
+        <v>-0.364619223715565</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.490940121521031</v>
+        <v>2.539996873619738</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.582472182326716</v>
+        <v>-4.476803298372129</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9204988191163657</v>
+        <v>0.9627663726982008</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.2519480054793148</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.553618560974503</v>
+        <v>2.602675313073211</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.470095181144043</v>
+        <v>-4.364426297189456</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9709409154201021</v>
+        <v>1.013208469001937</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.2519480054793148</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.559109856805171</v>
+        <v>2.608166608903878</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.668329750030774</v>
+        <v>-4.562660866076187</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.903144289633949</v>
+        <v>0.9454118432157839</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5319438278638909</v>
+        <v>-0.4501825743660454</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.451666317241671</v>
+        <v>2.500723069340379</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.751331031056053</v>
+        <v>-4.645662147101466</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7082994972244907</v>
+        <v>0.7505670508063256</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.4687534588932191</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.278879506526021</v>
+        <v>2.327936258624728</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.592136758999477</v>
+        <v>-4.486467875044889</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8921268667663269</v>
+        <v>0.9343944203481618</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.4687534588932191</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.399029167245226</v>
+        <v>2.448085919343934</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.678735341980579</v>
+        <v>-4.573066458025992</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8720004596762088</v>
+        <v>0.9142680132580436</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.4687534588932191</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.413542193347549</v>
+        <v>2.462598945446257</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.640351679422428</v>
+        <v>-4.534682795467841</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8847733660418378</v>
+        <v>0.9270409196236729</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.4303697963350679</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.433991832224809</v>
+        <v>2.483048584323516</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.422475410749803</v>
+        <v>3.786051782600427</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.459148194610252</v>
+        <v>-4.455118448139392</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9539837888120106</v>
+        <v>0.9555956874003548</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.4303697963350679</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.430720861070111</v>
+        <v>2.479777613168818</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.1%</t>
+          <t>-597.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.7%</t>
+          <t>-276.8%</t>
         </is>
       </c>
     </row>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.786051782600427</v>
+        <v>3.786051782600426</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.455118448139392</v>
+        <v>-4.357566465432675</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9555956874003548</v>
+        <v>0.9946164804830415</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.4303697963350679</v>

--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.6%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.5%</t>
+          <t>440.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-597.3%</t>
+          <t>-624.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-59.6%</t>
+          <t>-201.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.8%</t>
+          <t>-287.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.3%</t>
+          <t>-159.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-267.0%</t>
+          <t>-275.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-198.0%</t>
+          <t>-203.0%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.913593271654345</v>
+        <v>-6.019262155608931</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.751630727947596</v>
+        <v>0.7093631743657616</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9545487057869879</v>
+        <v>-1.036309959284833</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.544695237450889</v>
+        <v>2.495638485352182</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.278720654293092</v>
+        <v>-6.384389538247677</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6048342898979286</v>
+        <v>0.5625667363160942</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.250859490086</v>
+        <v>-1.332620743583846</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.366163281877313</v>
+        <v>2.317106529778606</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.68730943147377</v>
+        <v>-6.792978315428355</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4401603230404163</v>
+        <v>0.3978927694585823</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.119771559583665</v>
+        <v>2.070714807484958</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.100291915614863</v>
+        <v>-7.205960799569449</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2701527618554396</v>
+        <v>0.2278852082736051</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.114956992055125</v>
+        <v>2.065900239956418</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.516683789901861</v>
+        <v>-7.622352673856446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1015900627495179</v>
+        <v>0.05932250916768389</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.112951042664003</v>
+        <v>2.063894290565296</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.893360800431705</v>
+        <v>-7.999029684386291</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.0388220507937409</v>
+        <v>-0.08108960437557489</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.123209733332682</v>
+        <v>2.074152981233975</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.239235622416514</v>
+        <v>-8.344904506371099</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1810724144419691</v>
+        <v>-0.2233399680238031</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.119309298478377</v>
+        <v>2.070252546379669</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.401377892879607</v>
+        <v>-8.507046776834192</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2475244025722052</v>
+        <v>-0.2897919561540396</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.117714218533378</v>
+        <v>2.06865746643467</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.698039234689805</v>
+        <v>-8.803708118644391</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3624099633670763</v>
+        <v>-0.4046775169489107</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.728191403000557</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.080247313022259</v>
+        <v>2.031190560923552</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.13138834280004</v>
+        <v>-9.237057226754626</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5397759111455738</v>
+        <v>-0.5820434647274078</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.728191403000557</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.076221008487856</v>
+        <v>2.027164256389149</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.514389731542671</v>
+        <v>-9.620058615497257</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6930785679642102</v>
+        <v>-0.7353461215460442</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.728191403000557</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.076118907166272</v>
+        <v>2.027062155067564</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.671788611755792</v>
+        <v>-9.777457495710378</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7534666040780285</v>
+        <v>-0.7957341576598624</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.885590283213679</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.984251095009829</v>
+        <v>1.935194342911122</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.03131893425979</v>
+        <v>-10.13698781821438</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8919284297815784</v>
+        <v>-0.9341959833634128</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.885590283213679</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.98960139830788</v>
+        <v>1.940544646209172</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.35771896292481</v>
+        <v>-10.46338784687939</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.014572421290407</v>
+        <v>-1.05683997487224</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.211990311878691</v>
+        <v>-2.293751565376537</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.801677401066049</v>
+        <v>1.752620648967342</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.576867930999</v>
+        <v>-10.68253681495359</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.099190257898317</v>
+        <v>-1.141457811480151</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.431139279952889</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.673229770843299</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.57317700604259</v>
+        <v>-10.67884588999718</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.097713887915753</v>
+        <v>-1.139981441497586</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.431139279952889</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.673229770843299</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.77743518137246</v>
+        <v>-10.88310406532704</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.173903960929056</v>
+        <v>-1.21617151451089</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.558778224566878</v>
+        <v>-2.640539478064723</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.602159601193548</v>
+        <v>1.553102849094841</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.99547295300363</v>
+        <v>-11.10114183695822</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.25663651509709</v>
+        <v>-1.298904068678925</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.733548992662777</v>
+        <v>-2.815310246160622</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.501779694820445</v>
+        <v>1.452722942721738</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.92200312133619</v>
+        <v>-11.02767200529077</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.21187688093669</v>
+        <v>-1.254144434518524</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.660079160995328</v>
+        <v>-2.741840414493173</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.561233295314335</v>
+        <v>1.512176543215628</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.09712753872273</v>
+        <v>-11.20279642267731</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.26737142714379</v>
+        <v>-1.309638980725625</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.835203578381872</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.470713865629926</v>
+        <v>1.421657113531219</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.33157963273722</v>
+        <v>-11.4372485166918</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.368371429651182</v>
+        <v>-1.410638983233016</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.835203578381872</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.46349470072833</v>
+        <v>1.414437948629623</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.61938347727446</v>
+        <v>-11.72505236122904</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.490165158240054</v>
+        <v>-1.532432711821888</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.12300742291911</v>
+        <v>-3.204768676416955</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.284140203232011</v>
+        <v>1.235083451133304</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.84920792443828</v>
+        <v>-11.95487680839287</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.580979147267027</v>
+        <v>-1.623246700848862</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.285654959989271</v>
+        <v>-3.367416213487116</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.187667470828471</v>
+        <v>1.138610718729764</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.08123684417454</v>
+        <v>-12.18690572812913</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.671096986532417</v>
+        <v>-1.713364540114252</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.347667657177694</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.153153581144532</v>
+        <v>1.104096829045825</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.02922133020573</v>
+        <v>-12.13489021416032</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.646300445258492</v>
+        <v>-1.688567998840326</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.347667657177694</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.157143916830933</v>
+        <v>1.108087164732225</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.17089317192985</v>
+        <v>-12.27656205588444</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.704444408846881</v>
+        <v>-1.746711962428716</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.347667657177694</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.155668689932191</v>
+        <v>1.106611937833484</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.12130232750502</v>
+        <v>-12.2269712114596</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.669554660912075</v>
+        <v>-1.71182221449391</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.29807681275286</v>
+        <v>-3.379838066250705</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.200476606751963</v>
+        <v>1.151419854653256</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.92215022026792</v>
+        <v>-12.0278191042225</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.602944951663919</v>
+        <v>-1.645212505245753</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.132754286803047</v>
+        <v>-3.214515540300892</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.286618988675168</v>
+        <v>1.237562236576461</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.69630506754851</v>
+        <v>-11.80197395150309</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.503027817539946</v>
+        <v>-1.54529537112178</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.090827611215883</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.321354067063675</v>
+        <v>1.272297314964968</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.57172641121092</v>
+        <v>-11.6773952951655</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.45205721044885</v>
+        <v>-1.494324764030684</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.090827611215883</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.322493211619734</v>
+        <v>1.273436459521027</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.6246216992552</v>
+        <v>-11.73029058320979</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.470581551504457</v>
+        <v>-1.512849105086292</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.085872265127437</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.328100193434909</v>
+        <v>1.279043441336202</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.34071296832645</v>
+        <v>-11.44638185228104</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.351284354894321</v>
+        <v>-1.393551908476155</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.085872265127437</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.333833897673546</v>
+        <v>1.284777145574839</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.26934657571681</v>
+        <v>-11.37501545967139</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.332475060244327</v>
+        <v>-1.374742613826162</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.014505872517789</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.36691647084547</v>
+        <v>1.317859718746762</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.00550970851274</v>
+        <v>-11.11117859246732</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.236823794675607</v>
+        <v>-1.279091348257441</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.014505872517789</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.357032989532562</v>
+        <v>1.307976237433855</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.73826790764434</v>
+        <v>-11.01317919264889</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.131761634827622</v>
+        <v>-1.241726148829442</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.014505872517789</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.355198429033188</v>
+        <v>1.306141676934481</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.61496197916612</v>
+        <v>-10.88987326417067</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.082739578409795</v>
+        <v>-1.192704092411615</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.925088201390226</v>
+        <v>-3.006849454888072</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.408548716736265</v>
+        <v>1.359491964637558</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.59100843819016</v>
+        <v>-10.86591972319471</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.072489655873918</v>
+        <v>-1.182454169875738</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.901134660414269</v>
+        <v>-2.982895913912114</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.423589347467333</v>
+        <v>1.374532595368626</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.32694849986737</v>
+        <v>-10.60185978487191</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9801259967065512</v>
+        <v>-1.090090510708372</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.637074722091473</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.568764994299259</v>
+        <v>1.519708242200551</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.619868876362528</v>
+        <v>-9.894780161367077</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7000811809649177</v>
+        <v>-0.8100456949667372</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.637074722091473</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.565977960638958</v>
+        <v>1.516921208540251</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.579684577996337</v>
+        <v>-9.854595863000887</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6836638377306001</v>
+        <v>-0.7936283517324196</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.596890423725282</v>
+        <v>-2.678651677223127</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.590432163546514</v>
+        <v>1.541375411447807</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.499614782458533</v>
+        <v>-9.774526067463082</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6522690982947212</v>
+        <v>-0.7622336122965407</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.516820628187478</v>
+        <v>-2.598581881685323</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.637840862089953</v>
+        <v>1.588784109991246</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.266133560228933</v>
+        <v>-9.541044845233483</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5509521805650293</v>
+        <v>-0.6609166945668488</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.283339405957879</v>
+        <v>-2.365100659455724</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.785854024265564</v>
+        <v>1.736797272166857</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.08642503008506</v>
+        <v>-9.361336315089609</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4819609788204389</v>
+        <v>-0.5919254928222584</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.226167901795183</v>
+        <v>-2.307929155293028</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.817264716450223</v>
+        <v>1.768207964351516</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.954149556454173</v>
+        <v>-9.229060841458722</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4336833026210569</v>
+        <v>-0.5436478166228764</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.093892428164297</v>
+        <v>-2.175653681662142</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.891997487375782</v>
+        <v>1.842940735277075</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.763549881781019</v>
+        <v>-9.038461166785568</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.354628372064159</v>
+        <v>-0.4645928860659785</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.903292753491144</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.00917235286731</v>
+        <v>1.960115600768603</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.514550083097438</v>
+        <v>-8.789461368101987</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2421221113670677</v>
+        <v>-0.3520866253688872</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.903292753491144</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.022078694090969</v>
+        <v>1.973021941992262</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.620140072870543</v>
+        <v>-8.895051357875092</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4123340368755279</v>
+        <v>-0.5222985508773479</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.008882743264248</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.830748770627888</v>
+        <v>1.781692018529181</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.63887497498914</v>
+        <v>-8.913786259993689</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3712836558458807</v>
+        <v>-0.4812481698477002</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.008882743264248</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.879293112504974</v>
+        <v>1.830236360406267</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.49093493358154</v>
+        <v>-8.765846218586089</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4319865619710086</v>
+        <v>-0.5419510759728281</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.988561827355691</v>
+        <v>-2.070323080853536</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.771606739361941</v>
+        <v>1.722549987263234</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.466706297192568</v>
+        <v>-8.741617582197117</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4310090936688975</v>
+        <v>-0.5409736076707174</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.964333190966718</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.777429934941846</v>
+        <v>1.728373182843139</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.423157890421876</v>
+        <v>-8.698069175426426</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.420550343055714</v>
+        <v>-0.530514857057534</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.964333190966718</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.770469322846753</v>
+        <v>1.721412570748046</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.181009496968018</v>
+        <v>-8.455920781972567</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3092286312930277</v>
+        <v>-0.4191931452948476</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.964333190966718</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.784931677227896</v>
+        <v>1.735874925129189</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.117780125199671</v>
+        <v>-8.39269141020422</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2894047621264937</v>
+        <v>-0.3993692761283136</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.964333190966718</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.779463797687091</v>
+        <v>1.730407045588384</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.99448899038254</v>
+        <v>-8.26940027538709</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2425902141890646</v>
+        <v>-0.3525547281908845</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.841042056149588</v>
+        <v>-1.922803309647434</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.850936572587946</v>
+        <v>1.801879820489239</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.973339791479097</v>
+        <v>-8.248251076483648</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2264295563903622</v>
+        <v>-0.3363940703921826</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.819892857246145</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.871327070167337</v>
+        <v>1.82227031806863</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.729574349495652</v>
+        <v>-8.004485634500202</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1331426712499337</v>
+        <v>-0.2431071852517541</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.819892857246145</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.867107778514388</v>
+        <v>1.818051026415681</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.465546282302393</v>
+        <v>-7.740457567306943</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.025407130452614</v>
+        <v>-0.1353716444544344</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.618027458430191</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.990351331723976</v>
+        <v>1.941294579625269</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.215695888353318</v>
+        <v>-7.490607173357868</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06727510211071808</v>
+        <v>-0.04268941189110231</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.618027458430191</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.983093406707678</v>
+        <v>1.934036654608971</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.039803795885886</v>
+        <v>-7.314715080890436</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1412310626183397</v>
+        <v>0.03126654861651934</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.618027458430191</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.986692530228327</v>
+        <v>1.93763577812962</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.868357332863423</v>
+        <v>-7.143268617867973</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2231371538818787</v>
+        <v>0.1131726398800583</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.446580995407728</v>
+        <v>-1.528342248905573</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.102887914096359</v>
+        <v>2.053831161997651</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.6433243331946</v>
+        <v>-6.91823561819915</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3121708313657048</v>
+        <v>0.2022063173638844</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.221547995738905</v>
+        <v>-1.30330924923675</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.236928191513949</v>
+        <v>2.187871439415242</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.428689955558193</v>
+        <v>-6.703601240562743</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4027193834745848</v>
+        <v>0.2927548694727644</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.006913618102498</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.370403619150111</v>
+        <v>2.321346867051404</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.335689914352295</v>
+        <v>-6.610601199356845</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4211136587407398</v>
+        <v>0.3111491447389194</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.006913618102498</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.351597877933906</v>
+        <v>2.302541125835199</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.095259417547434</v>
+        <v>-6.370170702551984</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5190289340875611</v>
+        <v>0.4090644200857407</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7664831212976377</v>
+        <v>-0.8482443747954833</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.4975992526417</v>
+        <v>2.448542500542993</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.852468609897989</v>
+        <v>-6.127379894902539</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6200745709821596</v>
+        <v>0.5101100569803392</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7664831212976377</v>
+        <v>-0.8482443747954833</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.50152856647652</v>
+        <v>2.452471814377813</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.736528760272804</v>
+        <v>-6.011440045277354</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.667129094749574</v>
+        <v>0.5571645807477532</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6896613902815139</v>
+        <v>-0.7714226437793594</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.548300189003534</v>
+        <v>2.499243436904827</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.493873171849641</v>
+        <v>-5.768784456854191</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7611894013388323</v>
+        <v>0.6512248873370119</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6896613902815139</v>
+        <v>-0.7714226437793594</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.545298260223528</v>
+        <v>2.496241508124821</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.27385237381263</v>
+        <v>-5.54876365881718</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8507767575642506</v>
+        <v>0.7408122435624303</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5484415452135336</v>
+        <v>-0.6302027987113792</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.63160920427493</v>
+        <v>2.582552452176223</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.074603743907821</v>
+        <v>-5.349515028912371</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9463703923279976</v>
+        <v>0.8364058783261772</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5484415452135336</v>
+        <v>-0.6302027987113792</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.647503387076754</v>
+        <v>2.598446634978046</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.915088640388452</v>
+        <v>-5.189999925393002</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.011322278176048</v>
+        <v>0.901357764174227</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3889264416941637</v>
+        <v>-0.4706876951920093</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.744358293628677</v>
+        <v>2.69530154152997</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.770416495288714</v>
+        <v>-5.045327780293264</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.079279238777382</v>
+        <v>0.969314724775562</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2442542965944263</v>
+        <v>-0.3260155500922718</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.84124968324996</v>
+        <v>2.792192931151253</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.830291322646406</v>
+        <v>-5.105202607650956</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.041366799235731</v>
+        <v>0.931402285233911</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3041291239521184</v>
+        <v>-0.385890377449964</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.79136227823677</v>
+        <v>2.742305526138063</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.743491824867398</v>
+        <v>-5.018403109871948</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.098487091669901</v>
+        <v>0.9885225776680802</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3041291239521184</v>
+        <v>-0.385890377449964</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.813762771559337</v>
+        <v>2.764706019460629</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.745961531329204</v>
+        <v>-5.020872816333754</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.09757161045859</v>
+        <v>0.9876070964567703</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3065988304139246</v>
+        <v>-0.3883600839117701</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.812353349055665</v>
+        <v>2.763296596956958</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.814331717653214</v>
+        <v>-5.089243002657764</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.081230458403688</v>
+        <v>0.9712659444018681</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.828925690952096</v>
+        <v>2.779868938853388</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.692915288026738</v>
+        <v>-4.967826573031288</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.12023373888617</v>
+        <v>1.01026922488435</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.819362399583987</v>
+        <v>2.77030564748528</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.723908447355443</v>
+        <v>-4.998819732359993</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9325460401950749</v>
+        <v>0.8225815261932545</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.644071964624374</v>
+        <v>2.595015212525666</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.548434187562973</v>
+        <v>-4.823345472567524</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.007302976103851</v>
+        <v>0.8973384621020302</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.648639196616162</v>
+        <v>2.599582444517454</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.659370440204222</v>
+        <v>-4.934281725208773</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9629399489341486</v>
+        <v>0.8529754349323282</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.648650670502959</v>
+        <v>2.599593918404252</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.862397017747456</v>
+        <v>-5.137308302752006</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8848607031367608</v>
+        <v>0.7748961891349406</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.500349708920943</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.529966109196925</v>
+        <v>2.480909357098217</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.704471418812163</v>
+        <v>-4.979382703816713</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9582033291430103</v>
+        <v>0.8482388151411899</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.500349708920943</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.540138495629057</v>
+        <v>2.49108174353035</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.852792672623291</v>
+        <v>-5.127703957627841</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8938210981924193</v>
+        <v>0.7838565841905987</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.500349708920943</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.535084766202917</v>
+        <v>2.48602801410421</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.853975757274352</v>
+        <v>-5.128887042278902</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8851236397765205</v>
+        <v>0.7751591257747004</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5059927573874545</v>
+        <v>-0.5877540108853001</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.523474712567536</v>
+        <v>2.474417960468829</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.730848050280269</v>
+        <v>-5.005759335284819</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9349265956072554</v>
+        <v>0.824962081605435</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5059927573874545</v>
+        <v>-0.5877540108853001</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.524026585600638</v>
+        <v>2.47496983350193</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.638037568829409</v>
+        <v>-4.912948853833959</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9013234800789649</v>
+        <v>0.7913589660771445</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4131822759365952</v>
+        <v>-0.4949435294344408</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.508985566362519</v>
+        <v>2.459928814263812</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.589474516608379</v>
+        <v>-4.864385801612929</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9226221768919776</v>
+        <v>0.8126576628901572</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.364619223715565</v>
+        <v>-0.4463804772134106</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.539996873619738</v>
+        <v>2.490940121521031</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.476803298372129</v>
+        <v>-4.751714583376679</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9627663726982008</v>
+        <v>0.8528018586963804</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2519480054793148</v>
+        <v>-0.3337092589771604</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.602675313073211</v>
+        <v>2.553618560974503</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.364426297189456</v>
+        <v>-4.639337582194006</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.013208469001937</v>
+        <v>0.9032439550001168</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2519480054793148</v>
+        <v>-0.3337092589771604</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.608166608903878</v>
+        <v>2.559109856805171</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.562660866076187</v>
+        <v>-4.837572151080737</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9454118432157839</v>
+        <v>0.8354473292139635</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4501825743660454</v>
+        <v>-0.5319438278638909</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.500723069340379</v>
+        <v>2.451666317241671</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.645662147101466</v>
+        <v>-4.920573432106016</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7505670508063256</v>
+        <v>0.6406025368045052</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4687534588932191</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.327936258624728</v>
+        <v>2.278879506526021</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.486467875044889</v>
+        <v>-4.761379160049439</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9343944203481618</v>
+        <v>0.8244299063463414</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4687534588932191</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.448085919343934</v>
+        <v>2.399029167245226</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.573066458025992</v>
+        <v>-4.847977743030542</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9142680132580436</v>
+        <v>0.8043034992562232</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4687534588932191</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.462598945446257</v>
+        <v>2.413542193347549</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.534682795467841</v>
+        <v>-4.809594080472391</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9270409196236729</v>
+        <v>0.8170764056218525</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4303697963350679</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.483048584323516</v>
+        <v>2.433991832224809</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.786051782600426</v>
+        <v>3.424326257254314</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.357566465432675</v>
+        <v>-4.632477750437225</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9946164804830415</v>
+        <v>0.8846519664812211</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4303697963350679</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.479777613168818</v>
+        <v>2.430720861070111</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-24.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>134.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.7%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-624.8%</t>
+          <t>-597.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-201.2%</t>
+          <t>-59.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-287.8%</t>
+          <t>-276.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.4%</t>
+          <t>-153.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.2%</t>
+          <t>-267.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-203.0%</t>
+          <t>-159.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1955"/>
+  <dimension ref="A1:G1956"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.019262155608931</v>
+        <v>-5.913593271654345</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7093631743657616</v>
+        <v>0.751630727947596</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.036309959284833</v>
+        <v>-0.9545487057869879</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.495638485352182</v>
+        <v>2.544695237450889</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.384389538247677</v>
+        <v>-6.278720654293092</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5625667363160942</v>
+        <v>0.6048342898979286</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.332620743583846</v>
+        <v>-1.250859490086</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.317106529778606</v>
+        <v>2.366163281877313</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.792978315428355</v>
+        <v>-6.68730943147377</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3978927694585823</v>
+        <v>0.4401603230404163</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.070714807484958</v>
+        <v>2.119771559583665</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.205960799569449</v>
+        <v>-7.100291915614863</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2278852082736051</v>
+        <v>0.2701527618554396</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.065900239956418</v>
+        <v>2.114956992055125</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.622352673856446</v>
+        <v>-7.516683789901861</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.05932250916768389</v>
+        <v>0.1015900627495179</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.063894290565296</v>
+        <v>2.112951042664003</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.999029684386291</v>
+        <v>-7.893360800431705</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08108960437557489</v>
+        <v>-0.0388220507937409</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.074152981233975</v>
+        <v>2.123209733332682</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.344904506371099</v>
+        <v>-8.239235622416514</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2233399680238031</v>
+        <v>-0.1810724144419691</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.070252546379669</v>
+        <v>2.119309298478377</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.401377892879607</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.2475244025722052</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.659448267266679</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.06865746643467</v>
+        <v>2.117714218533378</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.698039234689805</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.3624099633670763</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.728191403000557</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.031190560923552</v>
+        <v>2.080247313022259</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.13138834280004</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5397759111455738</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.728191403000557</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.027164256389149</v>
+        <v>2.076221008487856</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.514389731542671</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.6930785679642102</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.728191403000557</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.027062155067564</v>
+        <v>2.076118907166272</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.671788611755792</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.7534666040780285</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.885590283213679</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935194342911122</v>
+        <v>1.984251095009829</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-10.03131893425979</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.8919284297815784</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.885590283213679</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.940544646209172</v>
+        <v>1.98960139830788</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.35771896292481</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-1.014572421290407</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.293751565376537</v>
+        <v>-2.211990311878691</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.752620648967342</v>
+        <v>1.801677401066049</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.576867930999</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.099190257898317</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.431139279952889</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.624173018744592</v>
+        <v>1.673229770843299</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.57317700604259</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.097713887915753</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.431139279952889</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.624173018744592</v>
+        <v>1.673229770843299</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.77743518137246</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.173903960929056</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.640539478064723</v>
+        <v>-2.558778224566878</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.553102849094841</v>
+        <v>1.602159601193548</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-10.99547295300363</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.25663651509709</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.815310246160622</v>
+        <v>-2.733548992662777</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.452722942721738</v>
+        <v>1.501779694820445</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-10.92200312133619</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.21187688093669</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.741840414493173</v>
+        <v>-2.660079160995328</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.512176543215628</v>
+        <v>1.561233295314335</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.09712753872273</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.26737142714379</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.835203578381872</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.421657113531219</v>
+        <v>1.470713865629926</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.33157963273722</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.368371429651182</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.835203578381872</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.414437948629623</v>
+        <v>1.46349470072833</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.61938347727446</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.490165158240054</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.204768676416955</v>
+        <v>-3.12300742291911</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.235083451133304</v>
+        <v>1.284140203232011</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.84920792443828</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.580979147267027</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.367416213487116</v>
+        <v>-3.285654959989271</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.138610718729764</v>
+        <v>1.187667470828471</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.08123684417454</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.671096986532417</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.347667657177694</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.104096829045825</v>
+        <v>1.153153581144532</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-12.02922133020573</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.646300445258492</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.347667657177694</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.108087164732225</v>
+        <v>1.157143916830933</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.17089317192985</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.704444408846881</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.347667657177694</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.106611937833484</v>
+        <v>1.155668689932191</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.12130232750502</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.669554660912075</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.379838066250705</v>
+        <v>-3.29807681275286</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.151419854653256</v>
+        <v>1.200476606751963</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-11.92215022026792</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.602944951663919</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.214515540300892</v>
+        <v>-3.132754286803047</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.237562236576461</v>
+        <v>1.286618988675168</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.69630506754851</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.503027817539946</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.090827611215883</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.272297314964968</v>
+        <v>1.321354067063675</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.57172641121092</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.45205721044885</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.090827611215883</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.273436459521027</v>
+        <v>1.322493211619734</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.6246216992552</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.470581551504457</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.085872265127437</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.279043441336202</v>
+        <v>1.328100193434909</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.34071296832645</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.351284354894321</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.085872265127437</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.284777145574839</v>
+        <v>1.333833897673546</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37501545967139</v>
+        <v>-11.26934657571681</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.374742613826162</v>
+        <v>-1.332475060244327</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.014505872517789</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.317859718746762</v>
+        <v>1.36691647084547</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-11.00550970851274</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.236823794675607</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.014505872517789</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.307976237433855</v>
+        <v>1.357032989532562</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.01317919264889</v>
+        <v>-10.73826790764434</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.241726148829442</v>
+        <v>-1.131761634827622</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.014505872517789</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.306141676934481</v>
+        <v>1.355198429033188</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.88987326417067</v>
+        <v>-10.61496197916612</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.192704092411615</v>
+        <v>-1.082739578409795</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.006849454888072</v>
+        <v>-2.925088201390226</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.359491964637558</v>
+        <v>1.408548716736265</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.86591972319471</v>
+        <v>-10.59100843819016</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.182454169875738</v>
+        <v>-1.072489655873918</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.982895913912114</v>
+        <v>-2.901134660414269</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.374532595368626</v>
+        <v>1.423589347467333</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.60185978487191</v>
+        <v>-10.32694849986737</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.090090510708372</v>
+        <v>-0.9801259967065512</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.637074722091473</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.519708242200551</v>
+        <v>1.568764994299259</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.894780161367077</v>
+        <v>-9.619868876362528</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8100456949667372</v>
+        <v>-0.7000811809649177</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.637074722091473</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.516921208540251</v>
+        <v>1.565977960638958</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.854595863000887</v>
+        <v>-9.579684577996337</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7936283517324196</v>
+        <v>-0.6836638377306001</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.678651677223127</v>
+        <v>-2.596890423725282</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.541375411447807</v>
+        <v>1.590432163546514</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.774526067463082</v>
+        <v>-9.499614782458533</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7622336122965407</v>
+        <v>-0.6522690982947212</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.598581881685323</v>
+        <v>-2.516820628187478</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.588784109991246</v>
+        <v>1.637840862089953</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.541044845233483</v>
+        <v>-9.266133560228933</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6609166945668488</v>
+        <v>-0.5509521805650293</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.365100659455724</v>
+        <v>-2.283339405957879</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.736797272166857</v>
+        <v>1.785854024265564</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.361336315089609</v>
+        <v>-9.08642503008506</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5919254928222584</v>
+        <v>-0.4819609788204389</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.307929155293028</v>
+        <v>-2.226167901795183</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.768207964351516</v>
+        <v>1.817264716450223</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.229060841458722</v>
+        <v>-8.954149556454173</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5436478166228764</v>
+        <v>-0.4336833026210569</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.175653681662142</v>
+        <v>-2.093892428164297</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.842940735277075</v>
+        <v>1.891997487375782</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.038461166785568</v>
+        <v>-8.763549881781019</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4645928860659785</v>
+        <v>-0.354628372064159</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.985054006988989</v>
+        <v>-1.903292753491144</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.960115600768603</v>
+        <v>2.00917235286731</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.789461368101987</v>
+        <v>-8.514550083097438</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3520866253688872</v>
+        <v>-0.2421221113670677</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.985054006988989</v>
+        <v>-1.903292753491144</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.973021941992262</v>
+        <v>2.022078694090969</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.895051357875092</v>
+        <v>-8.620140072870543</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5222985508773479</v>
+        <v>-0.4123340368755279</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.008882743264248</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.781692018529181</v>
+        <v>1.830748770627888</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.913786259993689</v>
+        <v>-8.63887497498914</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4812481698477002</v>
+        <v>-0.3712836558458807</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.008882743264248</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.830236360406267</v>
+        <v>1.879293112504974</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.765846218586089</v>
+        <v>-8.49093493358154</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5419510759728281</v>
+        <v>-0.4319865619710086</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.070323080853536</v>
+        <v>-1.988561827355691</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.722549987263234</v>
+        <v>1.771606739361941</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.741617582197117</v>
+        <v>-8.466706297192568</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5409736076707174</v>
+        <v>-0.4310090936688975</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.046094444464564</v>
+        <v>-1.964333190966718</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.728373182843139</v>
+        <v>1.777429934941846</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.698069175426426</v>
+        <v>-8.423157890421876</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.530514857057534</v>
+        <v>-0.420550343055714</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.046094444464564</v>
+        <v>-1.964333190966718</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.721412570748046</v>
+        <v>1.770469322846753</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.455920781972567</v>
+        <v>-8.181009496968018</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4191931452948476</v>
+        <v>-0.3092286312930277</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.046094444464564</v>
+        <v>-1.964333190966718</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.735874925129189</v>
+        <v>1.784931677227896</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.39269141020422</v>
+        <v>-8.117780125199671</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3993692761283136</v>
+        <v>-0.2894047621264937</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.046094444464564</v>
+        <v>-1.964333190966718</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.730407045588384</v>
+        <v>1.779463797687091</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.26940027538709</v>
+        <v>-7.99448899038254</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3525547281908845</v>
+        <v>-0.2425902141890646</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.922803309647434</v>
+        <v>-1.841042056149588</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.801879820489239</v>
+        <v>1.850936572587946</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.248251076483648</v>
+        <v>-7.973339791479097</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3363940703921826</v>
+        <v>-0.2264295563903622</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.819892857246145</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.82227031806863</v>
+        <v>1.871327070167337</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-8.004485634500202</v>
+        <v>-7.729574349495652</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2431071852517541</v>
+        <v>-0.1331426712499337</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.819892857246145</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.818051026415681</v>
+        <v>1.867107778514388</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.740457567306943</v>
+        <v>-7.465546282302393</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1353716444544344</v>
+        <v>-0.025407130452614</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.618027458430191</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.941294579625269</v>
+        <v>1.990351331723976</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.490607173357868</v>
+        <v>-7.215695888353318</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.04268941189110231</v>
+        <v>0.06727510211071808</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.618027458430191</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.934036654608971</v>
+        <v>1.983093406707678</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.314715080890436</v>
+        <v>-7.039803795885886</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.03126654861651934</v>
+        <v>0.1412310626183397</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.618027458430191</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.93763577812962</v>
+        <v>1.986692530228327</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.143268617867973</v>
+        <v>-6.868357332863423</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1131726398800583</v>
+        <v>0.2231371538818787</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.528342248905573</v>
+        <v>-1.446580995407728</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.053831161997651</v>
+        <v>2.102887914096359</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.91823561819915</v>
+        <v>-6.6433243331946</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2022063173638844</v>
+        <v>0.3121708313657048</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.30330924923675</v>
+        <v>-1.221547995738905</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.187871439415242</v>
+        <v>2.236928191513949</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.703601240562743</v>
+        <v>-6.428689955558193</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2927548694727644</v>
+        <v>0.4027193834745848</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.006913618102498</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.321346867051404</v>
+        <v>2.370403619150111</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.610601199356845</v>
+        <v>-6.335689914352295</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3111491447389194</v>
+        <v>0.4211136587407398</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.006913618102498</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.302541125835199</v>
+        <v>2.351597877933906</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.370170702551984</v>
+        <v>-6.095259417547434</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4090644200857407</v>
+        <v>0.5190289340875611</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.7664831212976377</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.448542500542993</v>
+        <v>2.4975992526417</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.127379894902539</v>
+        <v>-5.852468609897989</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5101100569803392</v>
+        <v>0.6200745709821596</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.7664831212976377</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.452471814377813</v>
+        <v>2.50152856647652</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.011440045277354</v>
+        <v>-5.736528760272804</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5571645807477532</v>
+        <v>0.667129094749574</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.6896613902815139</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.499243436904827</v>
+        <v>2.548300189003534</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.768784456854191</v>
+        <v>-5.493873171849641</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6512248873370119</v>
+        <v>0.7611894013388323</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.6896613902815139</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.496241508124821</v>
+        <v>2.545298260223528</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.54876365881718</v>
+        <v>-5.27385237381263</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7408122435624303</v>
+        <v>0.8507767575642506</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.5484415452135336</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.582552452176223</v>
+        <v>2.63160920427493</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.349515028912371</v>
+        <v>-5.074603743907821</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8364058783261772</v>
+        <v>0.9463703923279976</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.5484415452135336</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.598446634978046</v>
+        <v>2.647503387076754</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.189999925393002</v>
+        <v>-4.915088640388452</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.901357764174227</v>
+        <v>1.011322278176048</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4706876951920093</v>
+        <v>-0.3889264416941637</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.69530154152997</v>
+        <v>2.744358293628677</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.045327780293264</v>
+        <v>-4.770416495288714</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.969314724775562</v>
+        <v>1.079279238777382</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3260155500922718</v>
+        <v>-0.2442542965944263</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.792192931151253</v>
+        <v>2.84124968324996</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.105202607650956</v>
+        <v>-4.830291322646406</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.931402285233911</v>
+        <v>1.041366799235731</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.3041291239521184</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.742305526138063</v>
+        <v>2.79136227823677</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.018403109871948</v>
+        <v>-4.743491824867398</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9885225776680802</v>
+        <v>1.098487091669901</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.3041291239521184</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.764706019460629</v>
+        <v>2.813762771559337</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.020872816333754</v>
+        <v>-4.745961531329204</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9876070964567703</v>
+        <v>1.09757161045859</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3883600839117701</v>
+        <v>-0.3065988304139246</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.763296596956958</v>
+        <v>2.812353349055665</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.089243002657764</v>
+        <v>-4.814331717653214</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9712659444018681</v>
+        <v>1.081230458403688</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.779868938853388</v>
+        <v>2.828925690952096</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.967826573031288</v>
+        <v>-4.692915288026738</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.01026922488435</v>
+        <v>1.12023373888617</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.77030564748528</v>
+        <v>2.819362399583987</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.998819732359993</v>
+        <v>-4.723908447355443</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8225815261932545</v>
+        <v>0.9325460401950749</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.595015212525666</v>
+        <v>2.644071964624374</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.823345472567524</v>
+        <v>-4.548434187562973</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8973384621020302</v>
+        <v>1.007302976103851</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.599582444517454</v>
+        <v>2.648639196616162</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.934281725208773</v>
+        <v>-4.659370440204222</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8529754349323282</v>
+        <v>0.9629399489341486</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.2973231313777096</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.599593918404252</v>
+        <v>2.648650670502959</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.137308302752006</v>
+        <v>-4.862397017747456</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7748961891349406</v>
+        <v>0.8848607031367608</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.500349708920943</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.480909357098217</v>
+        <v>2.529966109196925</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.979382703816713</v>
+        <v>-4.704471418812163</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8482388151411899</v>
+        <v>0.9582033291430103</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.500349708920943</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.49108174353035</v>
+        <v>2.540138495629057</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.127703957627841</v>
+        <v>-4.852792672623291</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7838565841905987</v>
+        <v>0.8938210981924193</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.500349708920943</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.48602801410421</v>
+        <v>2.535084766202917</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.128887042278902</v>
+        <v>-4.853975757274352</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7751591257747004</v>
+        <v>0.8851236397765205</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.5059927573874545</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.474417960468829</v>
+        <v>2.523474712567536</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.005759335284819</v>
+        <v>-4.730848050280269</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.824962081605435</v>
+        <v>0.9349265956072554</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.5059927573874545</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.47496983350193</v>
+        <v>2.524026585600638</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.912948853833959</v>
+        <v>-4.638037568829409</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7913589660771445</v>
+        <v>0.9013234800789649</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4949435294344408</v>
+        <v>-0.4131822759365952</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.459928814263812</v>
+        <v>2.508985566362519</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.864385801612929</v>
+        <v>-4.589474516608379</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8126576628901572</v>
+        <v>0.9226221768919776</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4463804772134106</v>
+        <v>-0.364619223715565</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.490940121521031</v>
+        <v>2.539996873619738</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.751714583376679</v>
+        <v>-4.476803298372129</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8528018586963804</v>
+        <v>0.9627663726982008</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.2519480054793148</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.553618560974503</v>
+        <v>2.602675313073211</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.639337582194006</v>
+        <v>-4.364426297189456</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9032439550001168</v>
+        <v>1.013208469001937</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.2519480054793148</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.559109856805171</v>
+        <v>2.608166608903878</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.837572151080737</v>
+        <v>-4.562660866076187</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8354473292139635</v>
+        <v>0.9454118432157839</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5319438278638909</v>
+        <v>-0.4501825743660454</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.451666317241671</v>
+        <v>2.500723069340379</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.920573432106016</v>
+        <v>-4.645662147101466</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6406025368045052</v>
+        <v>0.7505670508063256</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.4687534588932191</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.278879506526021</v>
+        <v>2.327936258624728</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.761379160049439</v>
+        <v>-4.486467875044889</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8244299063463414</v>
+        <v>0.9343944203481618</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.4687534588932191</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.399029167245226</v>
+        <v>2.448085919343934</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.847977743030542</v>
+        <v>-4.573066458025992</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8043034992562232</v>
+        <v>0.9142680132580436</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.4687534588932191</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.413542193347549</v>
+        <v>2.462598945446257</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.809594080472391</v>
+        <v>-4.534682795467841</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8170764056218525</v>
+        <v>0.9270409196236729</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.4303697963350679</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.433991832224809</v>
+        <v>2.483048584323516</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,45 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.424326257254314</v>
+        <v>3.751143622002488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.632477750437225</v>
+        <v>-4.357566465432675</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8846519664812211</v>
+        <v>0.9946164804830415</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.4303697963350679</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.430720861070111</v>
+        <v>2.479777613168818</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="2" t="n">
+        <v>45418</v>
+      </c>
+      <c r="B1956" t="n">
+        <v>3.785707076854234</v>
+      </c>
+      <c r="C1956" t="n">
+        <v>2.874273997224094</v>
+      </c>
+      <c r="D1956" t="n">
+        <v>-4.357566465432675</v>
+      </c>
+      <c r="E1956" t="n">
+        <v>0.9946164804830415</v>
+      </c>
+      <c r="F1956" t="n">
+        <v>-0.4303697963350679</v>
+      </c>
+      <c r="G1956" t="n">
+        <v>2.867337794210462</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,25 +811,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-58.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.5%</t>
+          <t>135.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.5%</t>
+          <t>440.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-597.3%</t>
+          <t>-624.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-59.6%</t>
+          <t>-200.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.8%</t>
+          <t>-287.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.3%</t>
+          <t>-155.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-267.0%</t>
+          <t>-275.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.3%</t>
+          <t>-193.9%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.913593271654345</v>
+        <v>-6.019262155608931</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.751630727947596</v>
+        <v>0.7093631743657616</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9545487057869879</v>
+        <v>-1.036309959284833</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.544695237450889</v>
+        <v>2.495638485352182</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.278720654293092</v>
+        <v>-6.384389538247677</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6048342898979286</v>
+        <v>0.5625667363160942</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.250859490086</v>
+        <v>-1.332620743583846</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.366163281877313</v>
+        <v>2.317106529778606</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.68730943147377</v>
+        <v>-6.792978315428355</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4401603230404163</v>
+        <v>0.3978927694585823</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.119771559583665</v>
+        <v>2.070714807484958</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.100291915614863</v>
+        <v>-7.205960799569449</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2701527618554396</v>
+        <v>0.2278852082736051</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.114956992055125</v>
+        <v>2.065900239956418</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.516683789901861</v>
+        <v>-7.622352673856446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1015900627495179</v>
+        <v>0.05932250916768389</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.112951042664003</v>
+        <v>2.063894290565296</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.893360800431705</v>
+        <v>-7.999029684386291</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.0388220507937409</v>
+        <v>-0.08108960437557489</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.123209733332682</v>
+        <v>2.074152981233975</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.239235622416514</v>
+        <v>-8.344904506371099</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1810724144419691</v>
+        <v>-0.2233399680238031</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.119309298478377</v>
+        <v>2.070252546379669</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.401377892879607</v>
+        <v>-8.507046776834192</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2475244025722052</v>
+        <v>-0.2897919561540396</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.659448267266679</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.117714218533378</v>
+        <v>2.06865746643467</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.698039234689805</v>
+        <v>-8.803708118644391</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3624099633670763</v>
+        <v>-0.4046775169489107</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.728191403000557</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.080247313022259</v>
+        <v>2.031190560923552</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.13138834280004</v>
+        <v>-9.237057226754626</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5397759111455738</v>
+        <v>-0.5820434647274078</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.728191403000557</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.076221008487856</v>
+        <v>2.027164256389149</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.514389731542671</v>
+        <v>-9.620058615497257</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6930785679642102</v>
+        <v>-0.7353461215460442</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.728191403000557</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.076118907166272</v>
+        <v>2.027062155067564</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.671788611755792</v>
+        <v>-9.777457495710378</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7534666040780285</v>
+        <v>-0.7957341576598624</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.885590283213679</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.984251095009829</v>
+        <v>1.935194342911122</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.03131893425979</v>
+        <v>-10.13698781821438</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8919284297815784</v>
+        <v>-0.9341959833634128</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.885590283213679</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.98960139830788</v>
+        <v>1.940544646209172</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.35771896292481</v>
+        <v>-10.46338784687939</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.014572421290407</v>
+        <v>-1.05683997487224</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.211990311878691</v>
+        <v>-2.293751565376537</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.801677401066049</v>
+        <v>1.752620648967342</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.576867930999</v>
+        <v>-10.68253681495359</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.099190257898317</v>
+        <v>-1.141457811480151</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.431139279952889</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.673229770843299</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.57317700604259</v>
+        <v>-10.67884588999718</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.097713887915753</v>
+        <v>-1.139981441497586</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.431139279952889</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.673229770843299</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.77743518137246</v>
+        <v>-10.88310406532704</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.173903960929056</v>
+        <v>-1.21617151451089</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.558778224566878</v>
+        <v>-2.640539478064723</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.602159601193548</v>
+        <v>1.553102849094841</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.99547295300363</v>
+        <v>-11.10114183695822</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.25663651509709</v>
+        <v>-1.298904068678925</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.733548992662777</v>
+        <v>-2.815310246160622</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.501779694820445</v>
+        <v>1.452722942721738</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.92200312133619</v>
+        <v>-11.02767200529077</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.21187688093669</v>
+        <v>-1.254144434518524</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.660079160995328</v>
+        <v>-2.741840414493173</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.561233295314335</v>
+        <v>1.512176543215628</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.09712753872273</v>
+        <v>-11.20279642267731</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.26737142714379</v>
+        <v>-1.309638980725625</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.835203578381872</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.470713865629926</v>
+        <v>1.421657113531219</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.33157963273722</v>
+        <v>-11.4372485166918</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.368371429651182</v>
+        <v>-1.410638983233016</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.835203578381872</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.46349470072833</v>
+        <v>1.414437948629623</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.61938347727446</v>
+        <v>-11.72505236122904</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.490165158240054</v>
+        <v>-1.532432711821888</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.12300742291911</v>
+        <v>-3.204768676416955</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.284140203232011</v>
+        <v>1.235083451133304</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.84920792443828</v>
+        <v>-11.95487680839287</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.580979147267027</v>
+        <v>-1.623246700848862</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.285654959989271</v>
+        <v>-3.367416213487116</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.187667470828471</v>
+        <v>1.138610718729764</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.08123684417454</v>
+        <v>-12.18690572812913</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.671096986532417</v>
+        <v>-1.713364540114252</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.347667657177694</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.153153581144532</v>
+        <v>1.104096829045825</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.02922133020573</v>
+        <v>-12.13489021416032</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.646300445258492</v>
+        <v>-1.688567998840326</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.347667657177694</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.157143916830933</v>
+        <v>1.108087164732225</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.17089317192985</v>
+        <v>-12.27656205588444</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.704444408846881</v>
+        <v>-1.746711962428716</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.347667657177694</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.155668689932191</v>
+        <v>1.106611937833484</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.12130232750502</v>
+        <v>-12.2269712114596</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.669554660912075</v>
+        <v>-1.71182221449391</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.29807681275286</v>
+        <v>-3.379838066250705</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.200476606751963</v>
+        <v>1.151419854653256</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.92215022026792</v>
+        <v>-12.0278191042225</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.602944951663919</v>
+        <v>-1.645212505245753</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.132754286803047</v>
+        <v>-3.214515540300892</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.286618988675168</v>
+        <v>1.237562236576461</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.69630506754851</v>
+        <v>-11.80197395150309</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.503027817539946</v>
+        <v>-1.54529537112178</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.090827611215883</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.321354067063675</v>
+        <v>1.272297314964968</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.57172641121092</v>
+        <v>-11.6773952951655</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.45205721044885</v>
+        <v>-1.494324764030684</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.090827611215883</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.322493211619734</v>
+        <v>1.273436459521027</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.6246216992552</v>
+        <v>-11.73029058320979</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.470581551504457</v>
+        <v>-1.512849105086292</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.085872265127437</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.328100193434909</v>
+        <v>1.279043441336202</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.34071296832645</v>
+        <v>-11.44638185228104</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.351284354894321</v>
+        <v>-1.393551908476155</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.085872265127437</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.333833897673546</v>
+        <v>1.284777145574839</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.26934657571681</v>
+        <v>-11.37501545967139</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.332475060244327</v>
+        <v>-1.374742613826162</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.014505872517789</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.36691647084547</v>
+        <v>1.317859718746762</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.00550970851274</v>
+        <v>-11.11117859246732</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.236823794675607</v>
+        <v>-1.279091348257441</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.014505872517789</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.357032989532562</v>
+        <v>1.307976237433855</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.73826790764434</v>
+        <v>-11.01317919264889</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.131761634827622</v>
+        <v>-1.241726148829442</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.014505872517789</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.355198429033188</v>
+        <v>1.306141676934481</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.61496197916612</v>
+        <v>-10.88987326417067</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.082739578409795</v>
+        <v>-1.192704092411615</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.925088201390226</v>
+        <v>-3.006849454888072</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.408548716736265</v>
+        <v>1.359491964637558</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.59100843819016</v>
+        <v>-10.86591972319471</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.072489655873918</v>
+        <v>-1.182454169875738</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.901134660414269</v>
+        <v>-2.982895913912114</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.423589347467333</v>
+        <v>1.374532595368626</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.32694849986737</v>
+        <v>-10.60185978487191</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9801259967065512</v>
+        <v>-1.090090510708372</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.637074722091473</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.568764994299259</v>
+        <v>1.519708242200551</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.619868876362528</v>
+        <v>-9.894780161367077</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7000811809649177</v>
+        <v>-0.8100456949667372</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.637074722091473</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.565977960638958</v>
+        <v>1.516921208540251</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.579684577996337</v>
+        <v>-9.854595863000887</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6836638377306001</v>
+        <v>-0.7936283517324196</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.596890423725282</v>
+        <v>-2.678651677223127</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.590432163546514</v>
+        <v>1.541375411447807</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.499614782458533</v>
+        <v>-9.774526067463082</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6522690982947212</v>
+        <v>-0.7622336122965407</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.516820628187478</v>
+        <v>-2.598581881685323</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.637840862089953</v>
+        <v>1.588784109991246</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.266133560228933</v>
+        <v>-9.541044845233483</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5509521805650293</v>
+        <v>-0.6609166945668488</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.283339405957879</v>
+        <v>-2.365100659455724</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.785854024265564</v>
+        <v>1.736797272166857</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.08642503008506</v>
+        <v>-9.361336315089609</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4819609788204389</v>
+        <v>-0.5919254928222584</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.226167901795183</v>
+        <v>-2.307929155293028</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.817264716450223</v>
+        <v>1.768207964351516</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.954149556454173</v>
+        <v>-9.229060841458722</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4336833026210569</v>
+        <v>-0.5436478166228764</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.093892428164297</v>
+        <v>-2.175653681662142</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.891997487375782</v>
+        <v>1.842940735277075</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.763549881781019</v>
+        <v>-9.038461166785568</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.354628372064159</v>
+        <v>-0.4645928860659785</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.903292753491144</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.00917235286731</v>
+        <v>1.960115600768603</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.514550083097438</v>
+        <v>-8.789461368101987</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2421221113670677</v>
+        <v>-0.3520866253688872</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.903292753491144</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.022078694090969</v>
+        <v>1.973021941992262</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.620140072870543</v>
+        <v>-8.895051357875092</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4123340368755279</v>
+        <v>-0.5222985508773479</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.008882743264248</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.830748770627888</v>
+        <v>1.781692018529181</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.63887497498914</v>
+        <v>-8.913786259993689</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3712836558458807</v>
+        <v>-0.4812481698477002</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.008882743264248</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.879293112504974</v>
+        <v>1.830236360406267</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.49093493358154</v>
+        <v>-8.765846218586089</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4319865619710086</v>
+        <v>-0.5419510759728281</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.988561827355691</v>
+        <v>-2.070323080853536</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.771606739361941</v>
+        <v>1.722549987263234</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.466706297192568</v>
+        <v>-8.741617582197117</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4310090936688975</v>
+        <v>-0.5409736076707174</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.964333190966718</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.777429934941846</v>
+        <v>1.728373182843139</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.423157890421876</v>
+        <v>-8.698069175426426</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.420550343055714</v>
+        <v>-0.530514857057534</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.964333190966718</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.770469322846753</v>
+        <v>1.721412570748046</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.181009496968018</v>
+        <v>-8.455920781972567</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3092286312930277</v>
+        <v>-0.4191931452948476</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.964333190966718</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.784931677227896</v>
+        <v>1.735874925129189</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.117780125199671</v>
+        <v>-8.39269141020422</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2894047621264937</v>
+        <v>-0.3993692761283136</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.964333190966718</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.779463797687091</v>
+        <v>1.730407045588384</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.99448899038254</v>
+        <v>-8.26940027538709</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2425902141890646</v>
+        <v>-0.3525547281908845</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.841042056149588</v>
+        <v>-1.922803309647434</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.850936572587946</v>
+        <v>1.801879820489239</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.973339791479097</v>
+        <v>-8.248251076483648</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2264295563903622</v>
+        <v>-0.3363940703921826</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.819892857246145</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.871327070167337</v>
+        <v>1.82227031806863</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.729574349495652</v>
+        <v>-8.004485634500202</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1331426712499337</v>
+        <v>-0.2431071852517541</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.819892857246145</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.867107778514388</v>
+        <v>1.818051026415681</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.465546282302393</v>
+        <v>-7.740457567306943</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.025407130452614</v>
+        <v>-0.1353716444544344</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.618027458430191</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.990351331723976</v>
+        <v>1.941294579625269</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.215695888353318</v>
+        <v>-7.490607173357868</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06727510211071808</v>
+        <v>-0.04268941189110231</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.618027458430191</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.983093406707678</v>
+        <v>1.934036654608971</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.039803795885886</v>
+        <v>-7.314715080890436</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1412310626183397</v>
+        <v>0.03126654861651934</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.618027458430191</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.986692530228327</v>
+        <v>1.93763577812962</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.868357332863423</v>
+        <v>-7.143268617867973</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2231371538818787</v>
+        <v>0.1131726398800583</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.446580995407728</v>
+        <v>-1.528342248905573</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.102887914096359</v>
+        <v>2.053831161997651</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.6433243331946</v>
+        <v>-6.91823561819915</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3121708313657048</v>
+        <v>0.2022063173638844</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.221547995738905</v>
+        <v>-1.30330924923675</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.236928191513949</v>
+        <v>2.187871439415242</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.428689955558193</v>
+        <v>-6.703601240562743</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4027193834745848</v>
+        <v>0.2927548694727644</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.006913618102498</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.370403619150111</v>
+        <v>2.321346867051404</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544784</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.335689914352295</v>
+        <v>-6.610601199356845</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4211136587407398</v>
+        <v>0.3111491447389194</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.006913618102498</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.351597877933906</v>
+        <v>2.302541125835199</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.095259417547434</v>
+        <v>-6.370170702551984</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5190289340875611</v>
+        <v>0.4090644200857407</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7664831212976377</v>
+        <v>-0.8482443747954833</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.4975992526417</v>
+        <v>2.448542500542993</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.852468609897989</v>
+        <v>-6.127379894902539</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6200745709821596</v>
+        <v>0.5101100569803392</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7664831212976377</v>
+        <v>-0.8482443747954833</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.50152856647652</v>
+        <v>2.452471814377813</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.736528760272804</v>
+        <v>-6.011440045277354</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.667129094749574</v>
+        <v>0.5571645807477532</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6896613902815139</v>
+        <v>-0.7714226437793594</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.548300189003534</v>
+        <v>2.499243436904827</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.493873171849641</v>
+        <v>-5.768784456854191</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7611894013388323</v>
+        <v>0.6512248873370119</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6896613902815139</v>
+        <v>-0.7714226437793594</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.545298260223528</v>
+        <v>2.496241508124821</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.27385237381263</v>
+        <v>-5.54876365881718</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8507767575642506</v>
+        <v>0.7408122435624303</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5484415452135336</v>
+        <v>-0.6302027987113792</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.63160920427493</v>
+        <v>2.582552452176223</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.074603743907821</v>
+        <v>-5.349515028912371</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9463703923279976</v>
+        <v>0.8364058783261772</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5484415452135336</v>
+        <v>-0.6302027987113792</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.647503387076754</v>
+        <v>2.598446634978046</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.915088640388452</v>
+        <v>-5.189999925393002</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.011322278176048</v>
+        <v>0.901357764174227</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3889264416941637</v>
+        <v>-0.4706876951920093</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.744358293628677</v>
+        <v>2.69530154152997</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.770416495288714</v>
+        <v>-5.045327780293264</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.079279238777382</v>
+        <v>0.969314724775562</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2442542965944263</v>
+        <v>-0.3260155500922718</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.84124968324996</v>
+        <v>2.792192931151253</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.830291322646406</v>
+        <v>-5.105202607650956</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.041366799235731</v>
+        <v>0.931402285233911</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3041291239521184</v>
+        <v>-0.385890377449964</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.79136227823677</v>
+        <v>2.742305526138063</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.743491824867398</v>
+        <v>-5.018403109871948</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.098487091669901</v>
+        <v>0.9885225776680802</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3041291239521184</v>
+        <v>-0.385890377449964</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.813762771559337</v>
+        <v>2.764706019460629</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.745961531329204</v>
+        <v>-5.020872816333754</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.09757161045859</v>
+        <v>0.9876070964567703</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3065988304139246</v>
+        <v>-0.3883600839117701</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.812353349055665</v>
+        <v>2.763296596956958</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.814331717653214</v>
+        <v>-5.089243002657764</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.081230458403688</v>
+        <v>0.9712659444018681</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.828925690952096</v>
+        <v>2.779868938853388</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.692915288026738</v>
+        <v>-4.967826573031288</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.12023373888617</v>
+        <v>1.01026922488435</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.819362399583987</v>
+        <v>2.77030564748528</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.723908447355443</v>
+        <v>-4.998819732359993</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9325460401950749</v>
+        <v>0.8225815261932545</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.644071964624374</v>
+        <v>2.595015212525666</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.548434187562973</v>
+        <v>-4.823345472567524</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.007302976103851</v>
+        <v>0.8973384621020302</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.648639196616162</v>
+        <v>2.599582444517454</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.659370440204222</v>
+        <v>-4.934281725208773</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9629399489341486</v>
+        <v>0.8529754349323282</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2973231313777096</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.648650670502959</v>
+        <v>2.599593918404252</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.862397017747456</v>
+        <v>-5.137308302752006</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8848607031367608</v>
+        <v>0.7748961891349406</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.500349708920943</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.529966109196925</v>
+        <v>2.480909357098217</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.704471418812163</v>
+        <v>-4.979382703816713</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9582033291430103</v>
+        <v>0.8482388151411899</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.500349708920943</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.540138495629057</v>
+        <v>2.49108174353035</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.852792672623291</v>
+        <v>-5.127703957627841</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8938210981924193</v>
+        <v>0.7838565841905987</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.500349708920943</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.535084766202917</v>
+        <v>2.48602801410421</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.853975757274352</v>
+        <v>-5.128887042278902</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8851236397765205</v>
+        <v>0.7751591257747004</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5059927573874545</v>
+        <v>-0.5877540108853001</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.523474712567536</v>
+        <v>2.474417960468829</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.730848050280269</v>
+        <v>-5.005759335284819</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9349265956072554</v>
+        <v>0.824962081605435</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5059927573874545</v>
+        <v>-0.5877540108853001</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.524026585600638</v>
+        <v>2.47496983350193</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.638037568829409</v>
+        <v>-4.912948853833959</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9013234800789649</v>
+        <v>0.7913589660771445</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4131822759365952</v>
+        <v>-0.4949435294344408</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.508985566362519</v>
+        <v>2.459928814263812</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.589474516608379</v>
+        <v>-4.864385801612929</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9226221768919776</v>
+        <v>0.8126576628901572</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.364619223715565</v>
+        <v>-0.4463804772134106</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.539996873619738</v>
+        <v>2.490940121521031</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.476803298372129</v>
+        <v>-4.751714583376679</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9627663726982008</v>
+        <v>0.8528018586963804</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2519480054793148</v>
+        <v>-0.3337092589771604</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.602675313073211</v>
+        <v>2.553618560974503</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.364426297189456</v>
+        <v>-4.639337582194006</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.013208469001937</v>
+        <v>0.9032439550001168</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2519480054793148</v>
+        <v>-0.3337092589771604</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.608166608903878</v>
+        <v>2.559109856805171</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.562660866076187</v>
+        <v>-4.837572151080737</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9454118432157839</v>
+        <v>0.8354473292139635</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4501825743660454</v>
+        <v>-0.5319438278638909</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.500723069340379</v>
+        <v>2.451666317241671</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.645662147101466</v>
+        <v>-4.920573432106016</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7505670508063256</v>
+        <v>0.6406025368045052</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4687534588932191</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.327936258624728</v>
+        <v>2.278879506526021</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.486467875044889</v>
+        <v>-4.761379160049439</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9343944203481618</v>
+        <v>0.8244299063463414</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4687534588932191</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.448085919343934</v>
+        <v>2.399029167245226</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.573066458025992</v>
+        <v>-4.847977743030542</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9142680132580436</v>
+        <v>0.8043034992562232</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4687534588932191</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.462598945446257</v>
+        <v>2.413542193347549</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.534682795467841</v>
+        <v>-4.809594080472391</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9270409196236729</v>
+        <v>0.8170764056218525</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4303697963350679</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.483048584323516</v>
+        <v>2.433991832224809</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.357566465432675</v>
+        <v>-4.632477750437225</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9946164804830415</v>
+        <v>0.8846519664812211</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4303697963350679</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.479777613168818</v>
+        <v>2.430720861070111</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.785707076854234</v>
+        <v>3.42755346320428</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.874273997224094</v>
+        <v>2.527907033522585</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.357566465432675</v>
+        <v>-4.632477750437225</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9946164804830415</v>
+        <v>0.8846519664812211</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4303697963350679</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.867337794210462</v>
+        <v>2.520970830508952</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,55 +811,55 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-58.8%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.4%</t>
+          <t>134.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.1%</t>
+          <t>444.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-624.8%</t>
+          <t>-616.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-44.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-200.7%</t>
+          <t>-106.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-287.8%</t>
+          <t>-284.2%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-154.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.2%</t>
+          <t>-271.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-193.9%</t>
+          <t>-164.5%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.384389538247677</v>
+        <v>-6.296549805770965</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5625667363160942</v>
+        <v>0.5977026293067791</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.332620743583846</v>
+        <v>-1.294031737430106</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.317106529778606</v>
+        <v>2.340259933470849</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.792978315428355</v>
+        <v>-6.705138582951644</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3978927694585823</v>
+        <v>0.4330286624492667</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.702620514610785</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.070714807484958</v>
+        <v>2.093868211177201</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.205960799569449</v>
+        <v>-7.118121067092738</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2278852082736051</v>
+        <v>0.2630211012642896</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.702620514610785</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.065900239956418</v>
+        <v>2.089053643648662</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.622352673856446</v>
+        <v>-7.534512941379735</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.05932250916768389</v>
+        <v>0.09445840215836832</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.702620514610785</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.063894290565296</v>
+        <v>2.087047694257539</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.999029684386291</v>
+        <v>-7.91118995190958</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08108960437557489</v>
+        <v>-0.04595371138489046</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.702620514610785</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.074152981233975</v>
+        <v>2.097306384926218</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.344904506371099</v>
+        <v>-8.257064773894388</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2233399680238031</v>
+        <v>-0.1882040750331186</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.702620514610785</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.070252546379669</v>
+        <v>2.093405950071913</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.419207044357481</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.2546560631633552</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.702620514610785</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.06865746643467</v>
+        <v>2.091810870126914</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.71586838616768</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.3695416239582263</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.771363650344663</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.031190560923552</v>
+        <v>2.054343964615795</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.149217494277915</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5469075717367233</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.771363650344663</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.027164256389149</v>
+        <v>2.050317660081392</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.532218883020546</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.7002102285553597</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.771363650344663</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.027062155067564</v>
+        <v>2.050215558759808</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.689617763233667</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.760598264669178</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.928762530557785</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935194342911122</v>
+        <v>1.958347746603366</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-10.04914808573767</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.8990600903727284</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.928762530557785</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.940544646209172</v>
+        <v>1.963698049901415</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.37554811440268</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-1.021704081881556</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.293751565376537</v>
+        <v>-2.255162559222798</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.752620648967342</v>
+        <v>1.775774052659585</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.59469708247688</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.106321918489467</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.474311527296995</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.624173018744592</v>
+        <v>1.647326422436836</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.59100615752047</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.104845548506902</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.474311527296995</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.624173018744592</v>
+        <v>1.647326422436836</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.79526433285033</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.181035621520206</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.640539478064723</v>
+        <v>-2.601950471910984</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.553102849094841</v>
+        <v>1.576256252787085</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-11.01330210448151</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.26376817568824</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.815310246160622</v>
+        <v>-2.776721240006883</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.452722942721738</v>
+        <v>1.475876346413981</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-10.93983227281406</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.219008541527839</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.741840414493173</v>
+        <v>-2.703251408339435</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.512176543215628</v>
+        <v>1.535329946907872</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.1149566902006</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.27450308773494</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.878375825725978</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.421657113531219</v>
+        <v>1.444810517223462</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.34940878421509</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.375503090242332</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.878375825725978</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.414437948629623</v>
+        <v>1.437591352321866</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.63721262875233</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.497296818831204</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.204768676416955</v>
+        <v>-3.166179670263217</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.235083451133304</v>
+        <v>1.258236854825547</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.86703707591616</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.588110807858177</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.367416213487116</v>
+        <v>-3.328827207333377</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.138610718729764</v>
+        <v>1.161764122422007</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.09906599565242</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.678228647123567</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.3908399045218</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.104096829045825</v>
+        <v>1.127250232738068</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-12.04705048168361</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.653432105849642</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.3908399045218</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.108087164732225</v>
+        <v>1.131240568424468</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.18872232340773</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.711576069438031</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.3908399045218</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.106611937833484</v>
+        <v>1.129765341525727</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.13913147898289</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.676686321503225</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.379838066250705</v>
+        <v>-3.341249060096966</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.151419854653256</v>
+        <v>1.1745732583455</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-11.93997937174579</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.610076612255069</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.214515540300892</v>
+        <v>-3.175926534147153</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.237562236576461</v>
+        <v>1.260715640268705</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.71413421902638</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.510159478131095</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.13399985855999</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.272297314964968</v>
+        <v>1.295450718657211</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.58955556268879</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.459188871039999</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.13399985855999</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.273436459521027</v>
+        <v>1.29658986321327</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.64245085073308</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.477713212095606</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.129044512471543</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.279043441336202</v>
+        <v>1.302196845028446</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.35854211980433</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.35841601548547</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.129044512471543</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.284777145574839</v>
+        <v>1.307930549267082</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37501545967139</v>
+        <v>-11.28717572719468</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.374742613826162</v>
+        <v>-1.339606720835476</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.057678119861895</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.317859718746762</v>
+        <v>1.341013122439006</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-11.02333885999061</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.243955455266756</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.057678119861895</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.307976237433855</v>
+        <v>1.331129641126098</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.01317919264889</v>
+        <v>-10.92533946017218</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.241726148829442</v>
+        <v>-1.206590255838756</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.057678119861895</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.306141676934481</v>
+        <v>1.329295080626725</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.88987326417067</v>
+        <v>-10.80203353169396</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.192704092411615</v>
+        <v>-1.157568199420929</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.006849454888072</v>
+        <v>-2.968260448734333</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.359491964637558</v>
+        <v>1.382645368329801</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.86591972319471</v>
+        <v>-10.778079990718</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.182454169875738</v>
+        <v>-1.147318276885053</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.982895913912114</v>
+        <v>-2.944306907758375</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.374532595368626</v>
+        <v>1.397685999060869</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.60185978487191</v>
+        <v>-10.5140200523952</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.090090510708372</v>
+        <v>-1.054954617717686</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.680246969435579</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.519708242200551</v>
+        <v>1.542861645892795</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.894780161367077</v>
+        <v>-9.806940428890364</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8100456949667372</v>
+        <v>-0.7749098019760519</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.680246969435579</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.516921208540251</v>
+        <v>1.540074612232494</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.854595863000887</v>
+        <v>-9.766756130524174</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7936283517324196</v>
+        <v>-0.7584924587417343</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.678651677223127</v>
+        <v>-2.640062671069388</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.541375411447807</v>
+        <v>1.56452881514005</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.774526067463082</v>
+        <v>-9.686686334986369</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7622336122965407</v>
+        <v>-0.7270977193058559</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.598581881685323</v>
+        <v>-2.559992875531584</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.588784109991246</v>
+        <v>1.611937513683489</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.541044845233483</v>
+        <v>-9.45320511275677</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6609166945668488</v>
+        <v>-0.6257808015761634</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.365100659455724</v>
+        <v>-2.326511653301985</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.736797272166857</v>
+        <v>1.759950675859101</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.361336315089609</v>
+        <v>-9.273496582612896</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5919254928222584</v>
+        <v>-0.5567895998315735</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.307929155293028</v>
+        <v>-2.269340149139289</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.768207964351516</v>
+        <v>1.791361368043759</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.229060841458722</v>
+        <v>-9.141221108982009</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5436478166228764</v>
+        <v>-0.5085119236321916</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.175653681662142</v>
+        <v>-2.137064675508403</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.842940735277075</v>
+        <v>1.866094138969318</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.038461166785568</v>
+        <v>-8.950621434308855</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4645928860659785</v>
+        <v>-0.4294569930752932</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.985054006988989</v>
+        <v>-1.94646500083525</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.960115600768603</v>
+        <v>1.983269004460846</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.789461368101987</v>
+        <v>-8.701621635625274</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3520866253688872</v>
+        <v>-0.3169507323782024</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.985054006988989</v>
+        <v>-1.94646500083525</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.973021941992262</v>
+        <v>1.996175345684505</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.895051357875092</v>
+        <v>-8.807211625398379</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5222985508773479</v>
+        <v>-0.4871626578866626</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.052054990608355</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.781692018529181</v>
+        <v>1.804845422221424</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.913786259993689</v>
+        <v>-8.825946527516976</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4812481698477002</v>
+        <v>-0.4461122768570149</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.052054990608355</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.830236360406267</v>
+        <v>1.85338976409851</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.765846218586089</v>
+        <v>-8.678006486109377</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5419510759728281</v>
+        <v>-0.5068151829821428</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.070323080853536</v>
+        <v>-2.031734074699797</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.722549987263234</v>
+        <v>1.745703390955477</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.741617582197117</v>
+        <v>-8.653777849720404</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5409736076707174</v>
+        <v>-0.5058377146800321</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.007505438310825</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.728373182843139</v>
+        <v>1.751526586535382</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.698069175426426</v>
+        <v>-8.610229442949713</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.530514857057534</v>
+        <v>-0.4953789640668487</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.007505438310825</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.721412570748046</v>
+        <v>1.744565974440289</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.455920781972567</v>
+        <v>-8.368081049495855</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4191931452948476</v>
+        <v>-0.3840572523041623</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.007505438310825</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.735874925129189</v>
+        <v>1.759028328821432</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.39269141020422</v>
+        <v>-8.304851677727507</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3993692761283136</v>
+        <v>-0.3642333831376283</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.007505438310825</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.730407045588384</v>
+        <v>1.753560449280627</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.26940027538709</v>
+        <v>-8.181560542910377</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3525547281908845</v>
+        <v>-0.3174188352001996</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.922803309647434</v>
+        <v>-1.884214303493695</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.801879820489239</v>
+        <v>1.825033224181482</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.248251076483648</v>
+        <v>-8.160411344006935</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3363940703921826</v>
+        <v>-0.3012581774014973</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.863065104590251</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.82227031806863</v>
+        <v>1.845423721760873</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-8.004485634500202</v>
+        <v>-7.91664590202349</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2431071852517541</v>
+        <v>-0.2079712922610688</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.863065104590251</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.818051026415681</v>
+        <v>1.841204430107924</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.740457567306943</v>
+        <v>-7.652617834830231</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1353716444544344</v>
+        <v>-0.1002357514637491</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.661199705774298</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.941294579625269</v>
+        <v>1.964447983317512</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.490607173357868</v>
+        <v>-7.402767440881156</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.04268941189110231</v>
+        <v>-0.007553518900417</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.661199705774298</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.934036654608971</v>
+        <v>1.957190058301214</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.314715080890436</v>
+        <v>-7.226875348413724</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.03126654861651934</v>
+        <v>0.06640244160720421</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.661199705774298</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.93763577812962</v>
+        <v>1.960789181821863</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.143268617867973</v>
+        <v>-7.055428885391261</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1131726398800583</v>
+        <v>0.1483085328707436</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.528342248905573</v>
+        <v>-1.489753242751835</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.053831161997651</v>
+        <v>2.076984565689895</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.91823561819915</v>
+        <v>-6.830395885722438</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2022063173638844</v>
+        <v>0.2373422103545697</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.30330924923675</v>
+        <v>-1.264720243083012</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.187871439415242</v>
+        <v>2.211024843107485</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.703601240562743</v>
+        <v>-6.615761508086031</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2927548694727644</v>
+        <v>0.3278907624634497</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.050085865446605</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.321346867051404</v>
+        <v>2.344500270743647</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.610601199356845</v>
+        <v>-6.522761466880133</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3111491447389194</v>
+        <v>0.3462850377296047</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.050085865446605</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.302541125835199</v>
+        <v>2.325694529527443</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.370170702551984</v>
+        <v>-6.282330970075273</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4090644200857407</v>
+        <v>0.444200313076426</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.8096553686417445</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.448542500542993</v>
+        <v>2.471695904235236</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.127379894902539</v>
+        <v>-6.039540162425827</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5101100569803392</v>
+        <v>0.5452459499710245</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.8096553686417445</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.452471814377813</v>
+        <v>2.475625218070056</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.011440045277354</v>
+        <v>-5.923600312800642</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5571645807477532</v>
+        <v>0.5923004737384385</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.7328336376256206</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.499243436904827</v>
+        <v>2.522396840597071</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.768784456854191</v>
+        <v>-5.680944724377479</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6512248873370119</v>
+        <v>0.6863607803276972</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.7328336376256206</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.496241508124821</v>
+        <v>2.519394911817064</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.54876365881718</v>
+        <v>-5.460923926340469</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7408122435624303</v>
+        <v>0.7759481365531156</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.5916137925576404</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.582552452176223</v>
+        <v>2.605705855868466</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.349515028912371</v>
+        <v>-5.261675296435659</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8364058783261772</v>
+        <v>0.8715417713168625</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.5916137925576404</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.598446634978046</v>
+        <v>2.62160003867029</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.189999925393002</v>
+        <v>-5.10216019291629</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.901357764174227</v>
+        <v>0.9364936571649123</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4706876951920093</v>
+        <v>-0.4320986890382704</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.69530154152997</v>
+        <v>2.718454945222213</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.045327780293264</v>
+        <v>-4.957488047816552</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.969314724775562</v>
+        <v>1.004450617766247</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3260155500922718</v>
+        <v>-0.287426543938533</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.792192931151253</v>
+        <v>2.815346334843496</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.105202607650956</v>
+        <v>-5.017362875174245</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.931402285233911</v>
+        <v>0.9665381782245959</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.3473013712962251</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.742305526138063</v>
+        <v>2.765458929830306</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.018403109871948</v>
+        <v>-4.930563377395236</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9885225776680802</v>
+        <v>1.023658470658765</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.3473013712962251</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.764706019460629</v>
+        <v>2.787859423152872</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.020872816333754</v>
+        <v>-4.933033083857042</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9876070964567703</v>
+        <v>1.022742989447455</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3883600839117701</v>
+        <v>-0.3497710777580313</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.763296596956958</v>
+        <v>2.786450000649201</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.089243002657764</v>
+        <v>-5.001403270181052</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9712659444018681</v>
+        <v>1.006401837392553</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.3404953787218163</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.779868938853388</v>
+        <v>2.803022342545632</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.967826573031288</v>
+        <v>-4.879986840554576</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.01026922488435</v>
+        <v>1.045405117875035</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.3404953787218163</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.77030564748528</v>
+        <v>2.793459051177523</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.998819732359993</v>
+        <v>-4.910979999883281</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8225815261932545</v>
+        <v>0.8577174191839396</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.3404953787218163</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.595015212525666</v>
+        <v>2.61816861621791</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.823345472567524</v>
+        <v>-4.735505740090812</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8973384621020302</v>
+        <v>0.9324743550927153</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.3404953787218163</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.599582444517454</v>
+        <v>2.622735848209698</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.934281725208773</v>
+        <v>-4.846441992732061</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8529754349323282</v>
+        <v>0.8881113279230133</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.3404953787218163</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.599593918404252</v>
+        <v>2.622747322096495</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.137308302752006</v>
+        <v>-5.049468570275294</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7748961891349406</v>
+        <v>0.8100320821256255</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.5435219562650497</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.480909357098217</v>
+        <v>2.504062760790461</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.979382703816713</v>
+        <v>-4.891542971340001</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8482388151411899</v>
+        <v>0.8833747081318752</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.5435219562650497</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.49108174353035</v>
+        <v>2.514235147222593</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.127703957627841</v>
+        <v>-5.039864225151129</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7838565841905987</v>
+        <v>0.818992477181284</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.5435219562650497</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.48602801410421</v>
+        <v>2.509181417796453</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.128887042278902</v>
+        <v>-5.04104730980219</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7751591257747004</v>
+        <v>0.8102950187653852</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.5491650047315613</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.474417960468829</v>
+        <v>2.497571364161072</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.005759335284819</v>
+        <v>-4.917919602808107</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.824962081605435</v>
+        <v>0.8600979745961201</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.5491650047315613</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.47496983350193</v>
+        <v>2.498123237194174</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.912948853833959</v>
+        <v>-4.825109121357247</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7913589660771445</v>
+        <v>0.8264948590678296</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4949435294344408</v>
+        <v>-0.4563545232807019</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.459928814263812</v>
+        <v>2.483082217956055</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.864385801612929</v>
+        <v>-4.776546069136217</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8126576628901572</v>
+        <v>0.8477935558808425</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4463804772134106</v>
+        <v>-0.4077914710596717</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.490940121521031</v>
+        <v>2.514093525213274</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.751714583376679</v>
+        <v>-4.663874850899967</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8528018586963804</v>
+        <v>0.8879377516870655</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.2951202528234215</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.553618560974503</v>
+        <v>2.576771964666747</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.639337582194006</v>
+        <v>-4.551497849717294</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9032439550001168</v>
+        <v>0.9383798479908019</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.2951202528234215</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.559109856805171</v>
+        <v>2.582263260497414</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.837572151080737</v>
+        <v>-4.749732418604025</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8354473292139635</v>
+        <v>0.8705832222046486</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5319438278638909</v>
+        <v>-0.4933548217101521</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.451666317241671</v>
+        <v>2.474819720933915</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.920573432106016</v>
+        <v>-4.832733699629304</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6406025368045052</v>
+        <v>0.6757384297951903</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.5119257062373259</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.278879506526021</v>
+        <v>2.302032910218264</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.761379160049439</v>
+        <v>-4.673539427572727</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8244299063463414</v>
+        <v>0.8595657993370267</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.5119257062373259</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.399029167245226</v>
+        <v>2.42218257093747</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.847977743030542</v>
+        <v>-4.76013801055383</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8043034992562232</v>
+        <v>0.8394393922469083</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.5119257062373259</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.413542193347549</v>
+        <v>2.436695597039793</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.809594080472391</v>
+        <v>-4.721754347995679</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8170764056218525</v>
+        <v>0.8522122986125376</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.4735420436791747</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.433991832224809</v>
+        <v>2.457145235917052</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.632477750437225</v>
+        <v>-4.544638017960513</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8846519664812211</v>
+        <v>0.9197878594719064</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.4735420436791747</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.430720861070111</v>
+        <v>2.453874264762354</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.42755346320428</v>
+        <v>3.823500859174535</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.527907033522585</v>
+        <v>2.822295778705269</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.632477750437225</v>
+        <v>-4.544638017960513</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8846519664812211</v>
+        <v>0.9197878594719064</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.4735420436791747</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.520970830508952</v>
+        <v>2.815359575691637</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>114.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.6%</t>
+          <t>134.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-56.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.3%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-616.0%</t>
+          <t>-596.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-106.3%</t>
+          <t>-58.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.2%</t>
+          <t>-276.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.3%</t>
+          <t>-154.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-271.3%</t>
+          <t>-270.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.296549805770965</v>
+        <v>-6.27116346000512</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5977026293067791</v>
+        <v>0.6078571676131173</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.294031737430106</v>
+        <v>-1.280622708377046</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.340259933470849</v>
+        <v>2.348305350902685</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.705138582951644</v>
+        <v>-6.679752237185799</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4330286624492667</v>
+        <v>0.4431832007556049</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.702620514610785</v>
+        <v>-1.689211485557724</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.093868211177201</v>
+        <v>2.101913628609037</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.118121067092738</v>
+        <v>-7.092734721326893</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2630211012642896</v>
+        <v>0.2731756395706277</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.702620514610785</v>
+        <v>-1.689211485557724</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.089053643648662</v>
+        <v>2.097099061080498</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.534512941379735</v>
+        <v>-7.50912659561389</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.09445840215836832</v>
+        <v>0.1046129404647065</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.702620514610785</v>
+        <v>-1.689211485557724</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.087047694257539</v>
+        <v>2.095093111689375</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.91118995190958</v>
+        <v>-7.885803606143734</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04595371138489046</v>
+        <v>-0.03579917307855229</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.702620514610785</v>
+        <v>-1.689211485557724</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.097306384926218</v>
+        <v>2.105351802358054</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.257064773894388</v>
+        <v>-8.231678428128543</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1882040750331186</v>
+        <v>-0.1780495367267805</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.702620514610785</v>
+        <v>-1.689211485557724</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.093405950071913</v>
+        <v>2.101451367503749</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.419207044357481</v>
+        <v>-8.393820698591636</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2546560631633552</v>
+        <v>-0.244501524857017</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.702620514610785</v>
+        <v>-1.689211485557724</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.091810870126914</v>
+        <v>2.09985628755875</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.71586838616768</v>
+        <v>-8.690482040401834</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3695416239582263</v>
+        <v>-0.3593870856518881</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.771363650344663</v>
+        <v>-1.757954621291603</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.054343964615795</v>
+        <v>2.062389382047631</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.149217494277915</v>
+        <v>-9.123831148512069</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5469075717367233</v>
+        <v>-0.5367530334303852</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.771363650344663</v>
+        <v>-1.757954621291603</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.050317660081392</v>
+        <v>2.058363077513228</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.532218883020546</v>
+        <v>-9.5068325372547</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7002102285553597</v>
+        <v>-0.6900556902490216</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.771363650344663</v>
+        <v>-1.757954621291603</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.050215558759808</v>
+        <v>2.058260976191644</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.689617763233667</v>
+        <v>-9.664231417467821</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.760598264669178</v>
+        <v>-0.7504437263628398</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.928762530557785</v>
+        <v>-1.915353501504724</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.958347746603366</v>
+        <v>1.966393164035201</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.04914808573767</v>
+        <v>-10.02376173997182</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8990600903727284</v>
+        <v>-0.8889055520663902</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.928762530557785</v>
+        <v>-1.915353501504724</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.963698049901415</v>
+        <v>1.971743467333252</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.37554811440268</v>
+        <v>-10.35016176863684</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.021704081881556</v>
+        <v>-1.011549543575218</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.255162559222798</v>
+        <v>-2.241753530169737</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.775774052659585</v>
+        <v>1.783819470091422</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.59469708247688</v>
+        <v>-10.56931073671103</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.106321918489467</v>
+        <v>-1.096167380183128</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.474311527296995</v>
+        <v>-2.460902498243934</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.647326422436836</v>
+        <v>1.655371839868672</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.59100615752047</v>
+        <v>-10.56561981175462</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.104845548506902</v>
+        <v>-1.094691010200564</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.474311527296995</v>
+        <v>-2.460902498243934</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.647326422436836</v>
+        <v>1.655371839868672</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.79526433285033</v>
+        <v>-10.76987798708449</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.181035621520206</v>
+        <v>-1.170881083213867</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.601950471910984</v>
+        <v>-2.588541442857923</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.576256252787085</v>
+        <v>1.584301670218921</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.01330210448151</v>
+        <v>-10.98791575871566</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.26376817568824</v>
+        <v>-1.253613637381902</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.776721240006883</v>
+        <v>-2.763312210953822</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.475876346413981</v>
+        <v>1.483921763845818</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.93983227281406</v>
+        <v>-10.91444592704821</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.219008541527839</v>
+        <v>-1.208854003221501</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.703251408339435</v>
+        <v>-2.689842379286374</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.535329946907872</v>
+        <v>1.543375364339708</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.1149566902006</v>
+        <v>-11.08957034443476</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.27450308773494</v>
+        <v>-1.264348549428602</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.878375825725978</v>
+        <v>-2.864966796672918</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.444810517223462</v>
+        <v>1.452855934655298</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.34940878421509</v>
+        <v>-11.32402243844925</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.375503090242332</v>
+        <v>-1.365348551935993</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.878375825725978</v>
+        <v>-2.864966796672918</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.437591352321866</v>
+        <v>1.445636769753702</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.63721262875233</v>
+        <v>-11.61182628298649</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.497296818831204</v>
+        <v>-1.487142280524866</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.166179670263217</v>
+        <v>-3.152770641210156</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.258236854825547</v>
+        <v>1.266282272257383</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.86703707591616</v>
+        <v>-11.84165073015031</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.588110807858177</v>
+        <v>-1.577956269551839</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.328827207333377</v>
+        <v>-3.315418178280316</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.161764122422007</v>
+        <v>1.169809539853843</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.09906599565242</v>
+        <v>-12.07367964988657</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.678228647123567</v>
+        <v>-1.668074108817229</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.3908399045218</v>
+        <v>-3.37743087546874</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.127250232738068</v>
+        <v>1.135295650169904</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.04705048168361</v>
+        <v>-12.02166413591776</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.653432105849642</v>
+        <v>-1.643277567543303</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.3908399045218</v>
+        <v>-3.37743087546874</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.131240568424468</v>
+        <v>1.139285985856305</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.18872232340773</v>
+        <v>-12.16333597764188</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.711576069438031</v>
+        <v>-1.701421531131693</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.3908399045218</v>
+        <v>-3.37743087546874</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.129765341525727</v>
+        <v>1.137810758957563</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.13913147898289</v>
+        <v>-12.11374513321705</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.676686321503225</v>
+        <v>-1.666531783196887</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.341249060096966</v>
+        <v>-3.327840031043906</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.1745732583455</v>
+        <v>1.182618675777336</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.93997937174579</v>
+        <v>-11.91459302597995</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.610076612255069</v>
+        <v>-1.599922073948731</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.175926534147153</v>
+        <v>-3.162517505094093</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.260715640268705</v>
+        <v>1.268761057700541</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.71413421902638</v>
+        <v>-11.68874787326054</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.510159478131095</v>
+        <v>-1.500004939824757</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.13399985855999</v>
+        <v>-3.120590829506929</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.295450718657211</v>
+        <v>1.303496136089048</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.58955556268879</v>
+        <v>-11.56416921692294</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.459188871039999</v>
+        <v>-1.449034332733661</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.13399985855999</v>
+        <v>-3.120590829506929</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.29658986321327</v>
+        <v>1.304635280645106</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.64245085073308</v>
+        <v>-11.61706450496723</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.477713212095606</v>
+        <v>-1.467558673789268</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.129044512471543</v>
+        <v>-3.115635483418483</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.302196845028446</v>
+        <v>1.310242262460282</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.35854211980433</v>
+        <v>-11.33315577403848</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.35841601548547</v>
+        <v>-1.348261477179132</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.129044512471543</v>
+        <v>-3.115635483418483</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.307930549267082</v>
+        <v>1.315975966698918</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.28717572719468</v>
+        <v>-11.26178938142883</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.339606720835476</v>
+        <v>-1.329452182529138</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.057678119861895</v>
+        <v>-3.044269090808835</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.341013122439006</v>
+        <v>1.349058539870842</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.02333885999061</v>
+        <v>-10.99795251422476</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.243955455266756</v>
+        <v>-1.233800916960418</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.057678119861895</v>
+        <v>-3.044269090808835</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.331129641126098</v>
+        <v>1.339175058557935</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.92533946017218</v>
+        <v>-10.73071071335637</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.206590255838756</v>
+        <v>-1.128738757112433</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.057678119861895</v>
+        <v>-3.044269090808835</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.329295080626725</v>
+        <v>1.337340498058561</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.80203353169396</v>
+        <v>-10.60740478487815</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.157568199420929</v>
+        <v>-1.079716700694606</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.968260448734333</v>
+        <v>-2.954851419681272</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.382645368329801</v>
+        <v>1.390690785761638</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.778079990718</v>
+        <v>-10.58345124390219</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.147318276885053</v>
+        <v>-1.069466778158729</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.944306907758375</v>
+        <v>-2.930897878705315</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.397685999060869</v>
+        <v>1.405731416492705</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.5140200523952</v>
+        <v>-10.31939130557939</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.054954617717686</v>
+        <v>-0.9771031189913622</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.680246969435579</v>
+        <v>-2.666837940382518</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.542861645892795</v>
+        <v>1.550907063324631</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.806940428890364</v>
+        <v>-9.612311682074555</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7749098019760519</v>
+        <v>-0.6970583032497286</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.680246969435579</v>
+        <v>-2.666837940382518</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.540074612232494</v>
+        <v>1.54812002966433</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.766756130524174</v>
+        <v>-9.572127383708365</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7584924587417343</v>
+        <v>-0.6806409600154111</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.640062671069388</v>
+        <v>-2.626653642016327</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.56452881514005</v>
+        <v>1.572574232571886</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.686686334986369</v>
+        <v>-9.49205758817056</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7270977193058559</v>
+        <v>-0.6492462205795322</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.559992875531584</v>
+        <v>-2.546583846478523</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.611937513683489</v>
+        <v>1.619982931115326</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.45320511275677</v>
+        <v>-9.258576365940961</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6257808015761634</v>
+        <v>-0.5479293028498402</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.326511653301985</v>
+        <v>-2.313102624248925</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.759950675859101</v>
+        <v>1.767996093290937</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.273496582612896</v>
+        <v>-9.078867835797087</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5567895998315735</v>
+        <v>-0.4789381011052498</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.269340149139289</v>
+        <v>-2.255931120086229</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.791361368043759</v>
+        <v>1.799406785475596</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.141221108982009</v>
+        <v>-8.9465923621662</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5085119236321916</v>
+        <v>-0.4306604249058679</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.137064675508403</v>
+        <v>-2.123655646455342</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.866094138969318</v>
+        <v>1.874139556401154</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.950621434308855</v>
+        <v>-8.755992687493046</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4294569930752932</v>
+        <v>-0.3516054943489699</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.94646500083525</v>
+        <v>-1.93305597178219</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.983269004460846</v>
+        <v>1.991314421892683</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.701621635625274</v>
+        <v>-8.506992888809465</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3169507323782024</v>
+        <v>-0.2390992336518787</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.94646500083525</v>
+        <v>-1.93305597178219</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.996175345684505</v>
+        <v>2.004220763116342</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.807211625398379</v>
+        <v>-8.61258287858257</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4871626578866626</v>
+        <v>-0.4093111591603389</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.052054990608355</v>
+        <v>-2.038645961555294</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.804845422221424</v>
+        <v>1.81289083965326</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.825946527516976</v>
+        <v>-8.631317780701167</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4461122768570149</v>
+        <v>-0.3682607781306917</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.052054990608355</v>
+        <v>-2.038645961555294</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.85338976409851</v>
+        <v>1.861435181530347</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.678006486109377</v>
+        <v>-8.483377739293568</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5068151829821428</v>
+        <v>-0.4289636842558195</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.031734074699797</v>
+        <v>-2.018325045646737</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.745703390955477</v>
+        <v>1.753748808387313</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.653777849720404</v>
+        <v>-8.459149102904595</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5058377146800321</v>
+        <v>-0.4279862159537084</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.007505438310825</v>
+        <v>-1.994096409257764</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.751526586535382</v>
+        <v>1.759572003967218</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.610229442949713</v>
+        <v>-8.415600696133904</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4953789640668487</v>
+        <v>-0.417527465340525</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.007505438310825</v>
+        <v>-1.994096409257764</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.744565974440289</v>
+        <v>1.752611391872125</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.368081049495855</v>
+        <v>-8.173452302680046</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3840572523041623</v>
+        <v>-0.3062057535778386</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.007505438310825</v>
+        <v>-1.994096409257764</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.759028328821432</v>
+        <v>1.767073746253268</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.304851677727507</v>
+        <v>-8.110222930911698</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3642333831376283</v>
+        <v>-0.2863818844113046</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.007505438310825</v>
+        <v>-1.994096409257764</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.753560449280627</v>
+        <v>1.761605866712463</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.181560542910377</v>
+        <v>-7.986931796094567</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3174188352001996</v>
+        <v>-0.2395673364738755</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.884214303493695</v>
+        <v>-1.870805274440634</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.825033224181482</v>
+        <v>1.833078641613319</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.160411344006935</v>
+        <v>-7.965782597191124</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3012581774014973</v>
+        <v>-0.2234066786751732</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.863065104590251</v>
+        <v>-1.849656075537191</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.845423721760873</v>
+        <v>1.85346913919271</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.91664590202349</v>
+        <v>-7.72201715520768</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2079712922610688</v>
+        <v>-0.1301197935347447</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.863065104590251</v>
+        <v>-1.849656075537191</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.841204430107924</v>
+        <v>1.849249847539761</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.652617834830231</v>
+        <v>-7.45798908801442</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1002357514637491</v>
+        <v>-0.02238425273742495</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.661199705774298</v>
+        <v>-1.647790676721237</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.964447983317512</v>
+        <v>1.972493400749348</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.402767440881156</v>
+        <v>-7.208138694065346</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.007553518900417</v>
+        <v>0.07029797982590713</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.661199705774298</v>
+        <v>-1.647790676721237</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.957190058301214</v>
+        <v>1.965235475733051</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.226875348413724</v>
+        <v>-7.032246601597913</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.06640244160720421</v>
+        <v>0.1442539403335288</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.661199705774298</v>
+        <v>-1.647790676721237</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.960789181821863</v>
+        <v>1.968834599253699</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.055428885391261</v>
+        <v>-6.86080013857545</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1483085328707436</v>
+        <v>0.2261600315970678</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.489753242751835</v>
+        <v>-1.476344213698774</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.076984565689895</v>
+        <v>2.085029983121731</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.830395885722438</v>
+        <v>-6.635767138906627</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2373422103545697</v>
+        <v>0.3151937090808938</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.264720243083012</v>
+        <v>-1.251311214029951</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.211024843107485</v>
+        <v>2.219070260539322</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.615761508086031</v>
+        <v>-6.42113276127022</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3278907624634497</v>
+        <v>0.4057422611897739</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.050085865446605</v>
+        <v>-1.036676836393544</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.344500270743647</v>
+        <v>2.352545688175483</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.522761466880133</v>
+        <v>-6.328132720064322</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3462850377296047</v>
+        <v>0.4241365364559289</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.050085865446605</v>
+        <v>-1.036676836393544</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.325694529527443</v>
+        <v>2.333739946959279</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.282330970075273</v>
+        <v>-6.087702223259462</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.444200313076426</v>
+        <v>0.5220518118027502</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8096553686417445</v>
+        <v>-0.7962463395886838</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.471695904235236</v>
+        <v>2.479741321667072</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.039540162425827</v>
+        <v>-5.844911415610016</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5452459499710245</v>
+        <v>0.6230974486973486</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8096553686417445</v>
+        <v>-0.7962463395886838</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.475625218070056</v>
+        <v>2.483670635501892</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.923600312800642</v>
+        <v>-5.728971565984831</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5923004737384385</v>
+        <v>0.6701519724647631</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7328336376256206</v>
+        <v>-0.71942460857256</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.522396840597071</v>
+        <v>2.530442258028907</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.680944724377479</v>
+        <v>-5.486315977561668</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6863607803276972</v>
+        <v>0.7642122790540213</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7328336376256206</v>
+        <v>-0.71942460857256</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.519394911817064</v>
+        <v>2.5274403292489</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.460923926340469</v>
+        <v>-5.266295179524658</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7759481365531156</v>
+        <v>0.8537996352794397</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5916137925576404</v>
+        <v>-0.5782047635045797</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.605705855868466</v>
+        <v>2.613751273300303</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.261675296435659</v>
+        <v>-5.067046549619849</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8715417713168625</v>
+        <v>0.9493932700431866</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5916137925576404</v>
+        <v>-0.5782047635045797</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.62160003867029</v>
+        <v>2.629645456102126</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.10216019291629</v>
+        <v>-4.907531446100479</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9364936571649123</v>
+        <v>1.014345155891237</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4320986890382704</v>
+        <v>-0.4186896599852098</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.718454945222213</v>
+        <v>2.72650036265405</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.957488047816552</v>
+        <v>-4.762859301000741</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.004450617766247</v>
+        <v>1.082302116492571</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.287426543938533</v>
+        <v>-0.2740175148854724</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.815346334843496</v>
+        <v>2.823391752275332</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.017362875174245</v>
+        <v>-4.822734128358434</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9665381782245959</v>
+        <v>1.04438967695092</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3473013712962251</v>
+        <v>-0.3338923422431645</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.765458929830306</v>
+        <v>2.773504347262143</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.930563377395236</v>
+        <v>-4.735934630579425</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.023658470658765</v>
+        <v>1.10150996938509</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3473013712962251</v>
+        <v>-0.3338923422431645</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.787859423152872</v>
+        <v>2.795904840584709</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.933033083857042</v>
+        <v>-4.738404337041231</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.022742989447455</v>
+        <v>1.100594488173779</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3497710777580313</v>
+        <v>-0.3363620487049707</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.786450000649201</v>
+        <v>2.794495418081037</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.001403270181052</v>
+        <v>-4.806774523365242</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.006401837392553</v>
+        <v>1.084253336118878</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3404953787218163</v>
+        <v>-0.3270863496687557</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.803022342545632</v>
+        <v>2.811067759977468</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.879986840554576</v>
+        <v>-4.685358093738765</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.045405117875035</v>
+        <v>1.123256616601359</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3404953787218163</v>
+        <v>-0.3270863496687557</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.793459051177523</v>
+        <v>2.801504468609359</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.910979999883281</v>
+        <v>-4.71635125306747</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8577174191839396</v>
+        <v>0.935568917910264</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3404953787218163</v>
+        <v>-0.3270863496687557</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.61816861621791</v>
+        <v>2.626214033649746</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.735505740090812</v>
+        <v>-4.540876993275001</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9324743550927153</v>
+        <v>1.01032585381904</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3404953787218163</v>
+        <v>-0.3270863496687557</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.622735848209698</v>
+        <v>2.630781265641534</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.846441992732061</v>
+        <v>-4.65181324591625</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8881113279230133</v>
+        <v>0.9659628266493376</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3404953787218163</v>
+        <v>-0.3270863496687557</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.622747322096495</v>
+        <v>2.630792739528331</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.049468570275294</v>
+        <v>-4.854839823459483</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8100320821256255</v>
+        <v>0.8878835808519498</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5435219562650497</v>
+        <v>-0.5301129272119891</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.504062760790461</v>
+        <v>2.512108178222297</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.891542971340001</v>
+        <v>-4.69691422452419</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8833747081318752</v>
+        <v>0.9612262068581994</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5435219562650497</v>
+        <v>-0.5301129272119891</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.514235147222593</v>
+        <v>2.522280564654429</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.039864225151129</v>
+        <v>-4.845235478335319</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.818992477181284</v>
+        <v>0.8968439759076083</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5435219562650497</v>
+        <v>-0.5301129272119891</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.509181417796453</v>
+        <v>2.51722683522829</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.04104730980219</v>
+        <v>-4.846418562986379</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8102950187653852</v>
+        <v>0.8881465174917096</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5491650047315613</v>
+        <v>-0.5357559756785006</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.497571364161072</v>
+        <v>2.505616781592908</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.917919602808107</v>
+        <v>-4.723290855992296</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8600979745961201</v>
+        <v>0.9379494733224445</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5491650047315613</v>
+        <v>-0.5357559756785006</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.498123237194174</v>
+        <v>2.50616865462601</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.825109121357247</v>
+        <v>-4.630480374541436</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8264948590678296</v>
+        <v>0.904346357794154</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4563545232807019</v>
+        <v>-0.4429454942276413</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.483082217956055</v>
+        <v>2.491127635387891</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.776546069136217</v>
+        <v>-4.581917322320407</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8477935558808425</v>
+        <v>0.9256450546071666</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4077914710596717</v>
+        <v>-0.3943824420066111</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.514093525213274</v>
+        <v>2.52213894264511</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.663874850899967</v>
+        <v>-4.469246104084156</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8879377516870655</v>
+        <v>0.9657892504133898</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2951202528234215</v>
+        <v>-0.2817112237703609</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.576771964666747</v>
+        <v>2.584817382098583</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.551497849717294</v>
+        <v>-4.356869102901483</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9383798479908019</v>
+        <v>1.016231346717126</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2951202528234215</v>
+        <v>-0.2817112237703609</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.582263260497414</v>
+        <v>2.590308677929251</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.749732418604025</v>
+        <v>-4.555103671788214</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8705832222046486</v>
+        <v>0.9484347209309729</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4933548217101521</v>
+        <v>-0.4799457926570915</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.474819720933915</v>
+        <v>2.482865138365751</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.832733699629304</v>
+        <v>-4.638104952813493</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6757384297951903</v>
+        <v>0.7535899285215146</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5119257062373259</v>
+        <v>-0.4985166771842652</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.302032910218264</v>
+        <v>2.3100783276501</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.673539427572727</v>
+        <v>-4.478910680756917</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8595657993370267</v>
+        <v>0.9374172980633508</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5119257062373259</v>
+        <v>-0.4985166771842652</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.42218257093747</v>
+        <v>2.430227988369306</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.76013801055383</v>
+        <v>-4.565509263738019</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8394393922469083</v>
+        <v>0.9172908909732327</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5119257062373259</v>
+        <v>-0.4985166771842652</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.436695597039793</v>
+        <v>2.444741014471629</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.721754347995679</v>
+        <v>-4.527125601179868</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8522122986125376</v>
+        <v>0.9300637973388619</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4735420436791747</v>
+        <v>-0.4601330146261141</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.457145235917052</v>
+        <v>2.465190653348889</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.544638017960513</v>
+        <v>-4.350009271144702</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9197878594719064</v>
+        <v>0.9976393581982306</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4735420436791747</v>
+        <v>-0.4601330146261141</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.453874264762354</v>
+        <v>2.461919682194191</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,19 +46533,19 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.823500859174535</v>
+        <v>3.823500859174536</v>
       </c>
       <c r="C1956" t="n">
         <v>2.822295778705269</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.544638017960513</v>
+        <v>-4.350009271144702</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9197878594719064</v>
+        <v>0.9976393581982306</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4735420436791747</v>
+        <v>-0.4601330146261141</v>
       </c>
       <c r="G1956" t="n">
         <v>2.815359575691637</v>

--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.5%</t>
+          <t>114.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.4%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.5%</t>
+          <t>440.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-596.6%</t>
+          <t>-606.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-58.7%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.5%</t>
+          <t>-280.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.0%</t>
+          <t>-157.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-270.0%</t>
+          <t>-275.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.5%</t>
+          <t>-203.0%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.27116346000512</v>
+        <v>-6.384389538247677</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6078571676131173</v>
+        <v>0.5625667363160942</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.280622708377046</v>
+        <v>-1.332620743583846</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.348305350902685</v>
+        <v>2.317106529778606</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.679752237185799</v>
+        <v>-6.792978315428355</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4431832007556049</v>
+        <v>0.3978927694585823</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.689211485557724</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.101913628609037</v>
+        <v>2.070714807484958</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.092734721326893</v>
+        <v>-7.205960799569449</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2731756395706277</v>
+        <v>0.2278852082736051</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.689211485557724</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.097099061080498</v>
+        <v>2.065900239956418</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.50912659561389</v>
+        <v>-7.622352673856446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1046129404647065</v>
+        <v>0.05932250916768389</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.689211485557724</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.095093111689375</v>
+        <v>2.063894290565296</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.885803606143734</v>
+        <v>-7.999029684386291</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.03579917307855229</v>
+        <v>-0.08108960437557489</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.689211485557724</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.105351802358054</v>
+        <v>2.074152981233975</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.231678428128543</v>
+        <v>-8.344904506371099</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1780495367267805</v>
+        <v>-0.2233399680238031</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.689211485557724</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.101451367503749</v>
+        <v>2.070252546379669</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.393820698591636</v>
+        <v>-8.507046776834192</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.244501524857017</v>
+        <v>-0.2897919561540396</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.689211485557724</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.09985628755875</v>
+        <v>2.06865746643467</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.690482040401834</v>
+        <v>-8.803708118644391</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3593870856518881</v>
+        <v>-0.4046775169489107</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.757954621291603</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.062389382047631</v>
+        <v>2.031190560923552</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.123831148512069</v>
+        <v>-9.237057226754626</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5367530334303852</v>
+        <v>-0.5820434647274078</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.757954621291603</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.058363077513228</v>
+        <v>2.027164256389149</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.5068325372547</v>
+        <v>-9.620058615497257</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6900556902490216</v>
+        <v>-0.7353461215460442</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.757954621291603</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.058260976191644</v>
+        <v>2.027062155067564</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.664231417467821</v>
+        <v>-9.777457495710378</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7504437263628398</v>
+        <v>-0.7957341576598624</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.915353501504724</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.966393164035201</v>
+        <v>1.935194342911122</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.02376173997182</v>
+        <v>-10.13698781821438</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8889055520663902</v>
+        <v>-0.9341959833634128</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.915353501504724</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.971743467333252</v>
+        <v>1.940544646209172</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.35016176863684</v>
+        <v>-10.46338784687939</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.011549543575218</v>
+        <v>-1.05683997487224</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.241753530169737</v>
+        <v>-2.293751565376537</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.783819470091422</v>
+        <v>1.752620648967342</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.56931073671103</v>
+        <v>-10.68253681495359</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.096167380183128</v>
+        <v>-1.141457811480151</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.460902498243934</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.655371839868672</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.56561981175462</v>
+        <v>-10.67884588999718</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.094691010200564</v>
+        <v>-1.139981441497586</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.460902498243934</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.655371839868672</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.76987798708449</v>
+        <v>-10.88310406532704</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.170881083213867</v>
+        <v>-1.21617151451089</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.588541442857923</v>
+        <v>-2.640539478064723</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.584301670218921</v>
+        <v>1.553102849094841</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.98791575871566</v>
+        <v>-11.10114183695822</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.253613637381902</v>
+        <v>-1.298904068678925</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.763312210953822</v>
+        <v>-2.815310246160622</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.483921763845818</v>
+        <v>1.452722942721738</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.91444592704821</v>
+        <v>-11.02767200529077</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.208854003221501</v>
+        <v>-1.254144434518524</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.689842379286374</v>
+        <v>-2.741840414493173</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.543375364339708</v>
+        <v>1.512176543215628</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.08957034443476</v>
+        <v>-11.20279642267731</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.264348549428602</v>
+        <v>-1.309638980725625</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.864966796672918</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.452855934655298</v>
+        <v>1.421657113531219</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.32402243844925</v>
+        <v>-11.4372485166918</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.365348551935993</v>
+        <v>-1.410638983233016</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.864966796672918</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.445636769753702</v>
+        <v>1.414437948629623</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.61182628298649</v>
+        <v>-11.72505236122904</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.487142280524866</v>
+        <v>-1.532432711821888</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.152770641210156</v>
+        <v>-3.204768676416955</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.266282272257383</v>
+        <v>1.235083451133304</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.84165073015031</v>
+        <v>-11.95487680839287</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.577956269551839</v>
+        <v>-1.623246700848862</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.315418178280316</v>
+        <v>-3.367416213487116</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.169809539853843</v>
+        <v>1.138610718729764</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.07367964988657</v>
+        <v>-12.18690572812913</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.668074108817229</v>
+        <v>-1.713364540114252</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.37743087546874</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.135295650169904</v>
+        <v>1.104096829045825</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.02166413591776</v>
+        <v>-12.13489021416032</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.643277567543303</v>
+        <v>-1.688567998840326</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.37743087546874</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.139285985856305</v>
+        <v>1.108087164732225</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.16333597764188</v>
+        <v>-12.27656205588444</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.701421531131693</v>
+        <v>-1.746711962428716</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.37743087546874</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.137810758957563</v>
+        <v>1.106611937833484</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.11374513321705</v>
+        <v>-12.2269712114596</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.666531783196887</v>
+        <v>-1.71182221449391</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.327840031043906</v>
+        <v>-3.379838066250705</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.182618675777336</v>
+        <v>1.151419854653256</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.91459302597995</v>
+        <v>-12.0278191042225</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.599922073948731</v>
+        <v>-1.645212505245753</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.162517505094093</v>
+        <v>-3.214515540300892</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.268761057700541</v>
+        <v>1.237562236576461</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.68874787326054</v>
+        <v>-11.80197395150309</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.500004939824757</v>
+        <v>-1.54529537112178</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.120590829506929</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.303496136089048</v>
+        <v>1.272297314964968</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.56416921692294</v>
+        <v>-11.6773952951655</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.449034332733661</v>
+        <v>-1.494324764030684</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.120590829506929</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.304635280645106</v>
+        <v>1.273436459521027</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.61706450496723</v>
+        <v>-11.73029058320979</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.467558673789268</v>
+        <v>-1.512849105086292</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.115635483418483</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.310242262460282</v>
+        <v>1.279043441336202</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.33315577403848</v>
+        <v>-11.44638185228104</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.348261477179132</v>
+        <v>-1.393551908476155</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.115635483418483</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.315975966698918</v>
+        <v>1.284777145574839</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.26178938142883</v>
+        <v>-11.37501545967139</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.329452182529138</v>
+        <v>-1.374742613826162</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.044269090808835</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.349058539870842</v>
+        <v>1.317859718746762</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.99795251422476</v>
+        <v>-11.11117859246732</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.233800916960418</v>
+        <v>-1.279091348257441</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.044269090808835</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.339175058557935</v>
+        <v>1.307976237433855</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.73071071335637</v>
+        <v>-10.84393679159892</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.128738757112433</v>
+        <v>-1.174029188409456</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.044269090808835</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.337340498058561</v>
+        <v>1.306141676934481</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60740478487815</v>
+        <v>-10.72063086312071</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.079716700694606</v>
+        <v>-1.125007131991629</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.954851419681272</v>
+        <v>-3.006849454888072</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.390690785761638</v>
+        <v>1.359491964637558</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.58345124390219</v>
+        <v>-10.69667732214475</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.069466778158729</v>
+        <v>-1.114757209455753</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.930897878705315</v>
+        <v>-2.982895913912114</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.405731416492705</v>
+        <v>1.374532595368626</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.31939130557939</v>
+        <v>-10.43261738382195</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9771031189913622</v>
+        <v>-1.022393550288386</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.666837940382518</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.550907063324631</v>
+        <v>1.519708242200551</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.612311682074555</v>
+        <v>-9.725537760317113</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6970583032497286</v>
+        <v>-0.7423487345467517</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.666837940382518</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.54812002966433</v>
+        <v>1.516921208540251</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.572127383708365</v>
+        <v>-9.685353461950923</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6806409600154111</v>
+        <v>-0.7259313913124341</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.626653642016327</v>
+        <v>-2.678651677223127</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.572574232571886</v>
+        <v>1.541375411447807</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.49205758817056</v>
+        <v>-9.605283666413118</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6492462205795322</v>
+        <v>-0.6945366518765557</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.546583846478523</v>
+        <v>-2.598581881685323</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.619982931115326</v>
+        <v>1.588784109991246</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.258576365940961</v>
+        <v>-9.371802444183519</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5479293028498402</v>
+        <v>-0.5932197341468632</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.313102624248925</v>
+        <v>-2.365100659455724</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.767996093290937</v>
+        <v>1.736797272166857</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.078867835797087</v>
+        <v>-9.192093914039646</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4789381011052498</v>
+        <v>-0.5242285324022733</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.255931120086229</v>
+        <v>-2.307929155293028</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.799406785475596</v>
+        <v>1.768207964351516</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.9465923621662</v>
+        <v>-9.059818440408758</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4306604249058679</v>
+        <v>-0.4759508562028913</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.123655646455342</v>
+        <v>-2.175653681662142</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.874139556401154</v>
+        <v>1.842940735277075</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.755992687493046</v>
+        <v>-8.869218765735605</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3516054943489699</v>
+        <v>-0.396895925645993</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.93305597178219</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.991314421892683</v>
+        <v>1.960115600768603</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.506992888809465</v>
+        <v>-8.620218967052024</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2390992336518787</v>
+        <v>-0.2843896649489017</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.93305597178219</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.004220763116342</v>
+        <v>1.973021941992262</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.61258287858257</v>
+        <v>-8.725808956825128</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4093111591603389</v>
+        <v>-0.4546015904573624</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.038645961555294</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.81289083965326</v>
+        <v>1.781692018529181</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.631317780701167</v>
+        <v>-8.744543858943725</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3682607781306917</v>
+        <v>-0.4135512094277147</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.038645961555294</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.861435181530347</v>
+        <v>1.830236360406267</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.483377739293568</v>
+        <v>-8.596603817536126</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4289636842558195</v>
+        <v>-0.4742541155528426</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.018325045646737</v>
+        <v>-2.070323080853536</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.753748808387313</v>
+        <v>1.722549987263234</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.459149102904595</v>
+        <v>-8.572375181147153</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4279862159537084</v>
+        <v>-0.4732766472507319</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.994096409257764</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.759572003967218</v>
+        <v>1.728373182843139</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.415600696133904</v>
+        <v>-8.528826774376462</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.417527465340525</v>
+        <v>-0.4628178966375485</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.994096409257764</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.752611391872125</v>
+        <v>1.721412570748046</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.173452302680046</v>
+        <v>-8.286678380922604</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3062057535778386</v>
+        <v>-0.3514961848748621</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.994096409257764</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.767073746253268</v>
+        <v>1.735874925129189</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.110222930911698</v>
+        <v>-8.223449009154256</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2863818844113046</v>
+        <v>-0.3316723157083281</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.994096409257764</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.761605866712463</v>
+        <v>1.730407045588384</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.986931796094567</v>
+        <v>-8.100157874337127</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2395673364738755</v>
+        <v>-0.2848577677708994</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.870805274440634</v>
+        <v>-1.922803309647434</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.833078641613319</v>
+        <v>1.801879820489239</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.965782597191124</v>
+        <v>-8.079008675433684</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2234066786751732</v>
+        <v>-0.2686971099721971</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.849656075537191</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.85346913919271</v>
+        <v>1.82227031806863</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.72201715520768</v>
+        <v>-7.83524323345024</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1301197935347447</v>
+        <v>-0.1754102248317686</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.849656075537191</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.849249847539761</v>
+        <v>1.818051026415681</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.45798908801442</v>
+        <v>-7.57121516625698</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.02238425273742495</v>
+        <v>-0.06767468403444887</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.647790676721237</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.972493400749348</v>
+        <v>1.941294579625269</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.208138694065346</v>
+        <v>-7.321364772307906</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.07029797982590713</v>
+        <v>0.02500754852888321</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.647790676721237</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.965235475733051</v>
+        <v>1.934036654608971</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.032246601597913</v>
+        <v>-7.145472679840474</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1442539403335288</v>
+        <v>0.09896350903650486</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.647790676721237</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.968834599253699</v>
+        <v>1.93763577812962</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.86080013857545</v>
+        <v>-6.97402621681801</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2261600315970678</v>
+        <v>0.1808696003000438</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.476344213698774</v>
+        <v>-1.528342248905573</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.085029983121731</v>
+        <v>2.053831161997651</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.635767138906627</v>
+        <v>-6.748993217149187</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3151937090808938</v>
+        <v>0.2699032777838699</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.251311214029951</v>
+        <v>-1.30330924923675</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.219070260539322</v>
+        <v>2.187871439415242</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.42113276127022</v>
+        <v>-6.53435883951278</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4057422611897739</v>
+        <v>0.3604518298927499</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.036676836393544</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.352545688175483</v>
+        <v>2.321346867051404</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.328132720064322</v>
+        <v>-6.441358798306882</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4241365364559289</v>
+        <v>0.3788461051589049</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.036676836393544</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.333739946959279</v>
+        <v>2.302541125835199</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.087702223259462</v>
+        <v>-6.365035589141383</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5220518118027502</v>
+        <v>0.4111184654499818</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7962463395886838</v>
+        <v>-1.012351662434845</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.479741321667072</v>
+        <v>2.350078127959376</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.844911415610016</v>
+        <v>-6.122244781491938</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6230974486973486</v>
+        <v>0.5121641023445802</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7962463395886838</v>
+        <v>-1.012351662434845</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.483670635501892</v>
+        <v>2.354007441794196</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.728971565984831</v>
+        <v>-6.006304931866753</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6701519724647631</v>
+        <v>0.5592186261119942</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.71942460857256</v>
+        <v>-0.9355299314187211</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.530442258028907</v>
+        <v>2.40077906432121</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.486315977561668</v>
+        <v>-5.763649343443589</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7642122790540213</v>
+        <v>0.6532789327012534</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.71942460857256</v>
+        <v>-0.9355299314187211</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.5274403292489</v>
+        <v>2.397777135541204</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.266295179524658</v>
+        <v>-5.543628545406579</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8537996352794397</v>
+        <v>0.7428662889266717</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5782047635045797</v>
+        <v>-0.7943100863507409</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.613751273300303</v>
+        <v>2.484088079592606</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.067046549619849</v>
+        <v>-5.344379915501769</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9493932700431866</v>
+        <v>0.8384599236904187</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5782047635045797</v>
+        <v>-0.7943100863507409</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.629645456102126</v>
+        <v>2.499982262394429</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.907531446100479</v>
+        <v>-5.1848648119824</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.014345155891237</v>
+        <v>0.9034118095384684</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4186896599852098</v>
+        <v>-0.6347949828313709</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.72650036265405</v>
+        <v>2.596837168946353</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.762859301000741</v>
+        <v>-5.040192666882662</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.082302116492571</v>
+        <v>0.9713687701398031</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2740175148854724</v>
+        <v>-0.4901228377316335</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.823391752275332</v>
+        <v>2.693728558567635</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.822734128358434</v>
+        <v>-5.100067494240355</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.04438967695092</v>
+        <v>0.933456330598152</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3338923422431645</v>
+        <v>-0.5499976650893257</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.773504347262143</v>
+        <v>2.643841153554446</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.735934630579425</v>
+        <v>-5.013267996461346</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.10150996938509</v>
+        <v>0.9905766230323216</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3338923422431645</v>
+        <v>-0.5499976650893257</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.795904840584709</v>
+        <v>2.666241646877012</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.738404337041231</v>
+        <v>-5.015737702923152</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.100594488173779</v>
+        <v>0.9896611418210113</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3363620487049707</v>
+        <v>-0.5524673715511319</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.794495418081037</v>
+        <v>2.66483222437334</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.806774523365242</v>
+        <v>-5.084107889247163</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.084253336118878</v>
+        <v>0.9733199897661091</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3270863496687557</v>
+        <v>-0.543191672514917</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.811067759977468</v>
+        <v>2.681404566269772</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.685358093738765</v>
+        <v>-4.962691459620686</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.123256616601359</v>
+        <v>1.012323270248591</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3270863496687557</v>
+        <v>-0.543191672514917</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.801504468609359</v>
+        <v>2.671841274901663</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.71635125306747</v>
+        <v>-4.993684618949391</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.935568917910264</v>
+        <v>0.8246355715574958</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3270863496687557</v>
+        <v>-0.543191672514917</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.626214033649746</v>
+        <v>2.49655083994205</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.540876993275001</v>
+        <v>-4.818210359156922</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.01032585381904</v>
+        <v>0.8993925074662714</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3270863496687557</v>
+        <v>-0.543191672514917</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.630781265641534</v>
+        <v>2.501118071933838</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.65181324591625</v>
+        <v>-4.929146611798171</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9659628266493376</v>
+        <v>0.8550294802965692</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3270863496687557</v>
+        <v>-0.543191672514917</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.630792739528331</v>
+        <v>2.501129545820635</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.854839823459483</v>
+        <v>-5.132173189341404</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8878835808519498</v>
+        <v>0.7769502344991817</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5301129272119891</v>
+        <v>-0.7462182500581503</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.512108178222297</v>
+        <v>2.382444984514601</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.69691422452419</v>
+        <v>-4.974247590406111</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9612262068581994</v>
+        <v>0.8502928605054312</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5301129272119891</v>
+        <v>-0.7462182500581503</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.522280564654429</v>
+        <v>2.392617370946733</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.845235478335319</v>
+        <v>-5.122568844217239</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8968439759076083</v>
+        <v>0.7859106295548401</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5301129272119891</v>
+        <v>-0.7462182500581503</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.51722683522829</v>
+        <v>2.387563641520593</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.846418562986379</v>
+        <v>-5.1237519288683</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8881465174917096</v>
+        <v>0.7772131711389414</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5357559756785006</v>
+        <v>-0.7518612985246619</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.505616781592908</v>
+        <v>2.375953587885212</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.723290855992296</v>
+        <v>-5.000624221874217</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9379494733224445</v>
+        <v>0.8270161269696761</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5357559756785006</v>
+        <v>-0.7518612985246619</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.50616865462601</v>
+        <v>2.376505460918313</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.630480374541436</v>
+        <v>-4.907813740423357</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.904346357794154</v>
+        <v>0.7934130114413855</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4429454942276413</v>
+        <v>-0.6590508170738025</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.491127635387891</v>
+        <v>2.361464441680194</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.581917322320407</v>
+        <v>-4.859250688202327</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9256450546071666</v>
+        <v>0.8147117082543984</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3943824420066111</v>
+        <v>-0.6104877648527723</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.52213894264511</v>
+        <v>2.392475748937414</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.469246104084156</v>
+        <v>-4.746579469966077</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9657892504133898</v>
+        <v>0.8548559040606214</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2817112237703609</v>
+        <v>-0.4978165466165221</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.584817382098583</v>
+        <v>2.455154188390887</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.356869102901483</v>
+        <v>-4.634202468783404</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.016231346717126</v>
+        <v>0.9052980003643578</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2817112237703609</v>
+        <v>-0.4978165466165221</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.590308677929251</v>
+        <v>2.460645484221554</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.555103671788214</v>
+        <v>-4.832437037670135</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9484347209309729</v>
+        <v>0.8375013745782045</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4799457926570915</v>
+        <v>-0.6960511155032527</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.482865138365751</v>
+        <v>2.353201944658054</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.638104952813493</v>
+        <v>-4.915438318695414</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7535899285215146</v>
+        <v>0.6426565821687462</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4985166771842652</v>
+        <v>-0.7146220000304264</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.3100783276501</v>
+        <v>2.180415133942404</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.478910680756917</v>
+        <v>-4.756244046638837</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9374172980633508</v>
+        <v>0.8264839517105826</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4985166771842652</v>
+        <v>-0.7146220000304264</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.430227988369306</v>
+        <v>2.300564794661609</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.565509263738019</v>
+        <v>-4.84284262961994</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9172908909732327</v>
+        <v>0.8063575446204645</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4985166771842652</v>
+        <v>-0.7146220000304264</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.444741014471629</v>
+        <v>2.315077820763932</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.527125601179868</v>
+        <v>-4.804458967061789</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9300637973388619</v>
+        <v>0.8191304509860935</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4601330146261141</v>
+        <v>-0.6762383374722752</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.465190653348889</v>
+        <v>2.335527459641192</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.350009271144702</v>
+        <v>-4.627342637026623</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9976393581982306</v>
+        <v>0.8867060118454624</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4601330146261141</v>
+        <v>-0.6762383374722752</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.461919682194191</v>
+        <v>2.332256488486494</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.823500859174536</v>
+        <v>3.424595891804273</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.822295778705269</v>
+        <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.350009271144702</v>
+        <v>-4.444091756661597</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9976393581982306</v>
+        <v>0.960689755753386</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4601330146261141</v>
+        <v>-0.5145701909201984</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.815359575691637</v>
+        <v>2.429940768179653</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240506.xlsx
+++ b/tame_output/ON/bt/strategyON_20240506.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.0%</t>
+          <t>-605.9%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.2%</t>
+          <t>-280.1%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.4%</t>
+          <t>-275.3%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -46539,16 +46539,16 @@
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.444091756661597</v>
+        <v>-4.442913932859831</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.960689755753386</v>
+        <v>0.9611608852740923</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5145701909201984</v>
+        <v>-0.5135188591045265</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.429940768179653</v>
+        <v>2.430571567269056</v>
       </c>
     </row>
   </sheetData>
